--- a/dane.xlsx
+++ b/dane.xlsx
@@ -1,40 +1,227 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wikgl\Desktop\analiza\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CAFD0D7-9AB6-424A-961F-0B32C2C34DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="TABLICA" sheetId="2" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="53">
+  <si>
+    <t>Kod</t>
+  </si>
+  <si>
+    <t>Nazwa</t>
+  </si>
+  <si>
+    <t>ogółem</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - ogółem</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - niedostosowanie prędkości do warunków ruchu</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - nieprzestrzeganie pierwszeństwa przejazdu</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - nieprawidłowe wyprzedzanie</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - nieprawidłowe zachowanie wobec pieszych</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - niezachowanie bezpiecznej odległości między pojazdami</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - pozostałe</t>
+  </si>
+  <si>
+    <t>wina pieszych - ogółem</t>
+  </si>
+  <si>
+    <t>wina pieszych - nieostrożne wejście na jezdnię</t>
+  </si>
+  <si>
+    <t>wina pieszych - pozostałe</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>[szt.]</t>
+  </si>
+  <si>
+    <t>0000000</t>
+  </si>
+  <si>
+    <t>POLSKA</t>
+  </si>
+  <si>
+    <t>0200000</t>
+  </si>
+  <si>
+    <t>DOLNOŚLĄSKIE</t>
+  </si>
+  <si>
+    <t>0400000</t>
+  </si>
+  <si>
+    <t>KUJAWSKO-POMORSKIE</t>
+  </si>
+  <si>
+    <t>0600000</t>
+  </si>
+  <si>
+    <t>LUBELSKIE</t>
+  </si>
+  <si>
+    <t>0800000</t>
+  </si>
+  <si>
+    <t>LUBUSKIE</t>
+  </si>
+  <si>
+    <t>1000000</t>
+  </si>
+  <si>
+    <t>ŁÓDZKIE</t>
+  </si>
+  <si>
+    <t>1200000</t>
+  </si>
+  <si>
+    <t>MAŁOPOLSKIE</t>
+  </si>
+  <si>
+    <t>1400000</t>
+  </si>
+  <si>
+    <t>MAZOWIECKIE</t>
+  </si>
+  <si>
+    <t>1600000</t>
+  </si>
+  <si>
+    <t>OPOLSKIE</t>
+  </si>
+  <si>
+    <t>1800000</t>
+  </si>
+  <si>
+    <t>PODKARPACKIE</t>
+  </si>
+  <si>
+    <t>2000000</t>
+  </si>
+  <si>
+    <t>PODLASKIE</t>
+  </si>
+  <si>
+    <t>2200000</t>
+  </si>
+  <si>
+    <t>POMORSKIE</t>
+  </si>
+  <si>
+    <t>2400000</t>
+  </si>
+  <si>
+    <t>ŚLĄSKIE</t>
+  </si>
+  <si>
+    <t>2600000</t>
+  </si>
+  <si>
+    <t>ŚWIĘTOKRZYSKIE</t>
+  </si>
+  <si>
+    <t>2800000</t>
+  </si>
+  <si>
+    <t>WARMIŃSKO-MAZURSKIE</t>
+  </si>
+  <si>
+    <t>3000000</t>
+  </si>
+  <si>
+    <t>WIELKOPOLSKIE</t>
+  </si>
+  <si>
+    <t>3200000</t>
+  </si>
+  <si>
+    <t>ZACHODNIOPOMORSKIE</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
+      <charset val="238"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD3D3D3"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -46,100 +233,58 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Kolumna" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motyw pakietu Office">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Pakiet Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -147,44 +292,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Pakiet Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -211,14 +356,32 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -245,9 +408,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Pakiet Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -256,3475 +437,3659 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
+            <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:BE18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:BE22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Kod</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Nazwa</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ogółem_2020</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>ogółem_2021</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>ogółem_2022</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>ogółem_2023</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>ogółem_2024</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - ogółem_2020</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - ogółem_2021</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - ogółem_2022</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - ogółem_2023</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - ogółem_2024</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - niedostosowanie prędkości do warunków ruchu_2020</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - niedostosowanie prędkości do warunków ruchu_2021</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - niedostosowanie prędkości do warunków ruchu_2022</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - niedostosowanie prędkości do warunków ruchu_2023</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - niedostosowanie prędkości do warunków ruchu_2024</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - nieprzestrzeganie pierwszeństwa przejazdu_2020</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - nieprzestrzeganie pierwszeństwa przejazdu_2021</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - nieprzestrzeganie pierwszeństwa przejazdu_2022</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - nieprzestrzeganie pierwszeństwa przejazdu_2023</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - nieprzestrzeganie pierwszeństwa przejazdu_2024</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - nieprawidłowe wyprzedzanie_2020</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - nieprawidłowe wyprzedzanie_2021</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - nieprawidłowe wyprzedzanie_2022</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - nieprawidłowe wyprzedzanie_2023</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - nieprawidłowe wyprzedzanie_2024</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - nieprawidłowe zachowanie wobec pieszych_2020</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - nieprawidłowe zachowanie wobec pieszych_2021</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - nieprawidłowe zachowanie wobec pieszych_2022</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - nieprawidłowe zachowanie wobec pieszych_2023</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - nieprawidłowe zachowanie wobec pieszych_2024</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - niezachowanie bezpiecznej odległości między pojazdami_2020</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - niezachowanie bezpiecznej odległości między pojazdami_2021</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - niezachowanie bezpiecznej odległości między pojazdami_2022</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - niezachowanie bezpiecznej odległości między pojazdami_2023</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - niezachowanie bezpiecznej odległości między pojazdami_2024</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - pozostałe_2020</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - pozostałe_2021</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - pozostałe_2022</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - pozostałe_2023</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - pozostałe_2024</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>wina pieszych - ogółem_2020</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>wina pieszych - ogółem_2021</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>wina pieszych - ogółem_2022</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>wina pieszych - ogółem_2023</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>wina pieszych - ogółem_2024</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>wina pieszych - nieostrożne wejście na jezdnię_2020</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>wina pieszych - nieostrożne wejście na jezdnię_2021</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>wina pieszych - nieostrożne wejście na jezdnię_2022</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>wina pieszych - nieostrożne wejście na jezdnię_2023</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>wina pieszych - nieostrożne wejście na jezdnię_2024</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>wina pieszych - pozostałe_2020</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>wina pieszych - pozostałe_2021</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>wina pieszych - pozostałe_2022</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>wina pieszych - pozostałe_2023</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>wina pieszych - pozostałe_2024</t>
-        </is>
-      </c>
+    <row r="1" spans="1:57" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+      <c r="AA1" s="3"/>
+      <c r="AB1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC1" s="3"/>
+      <c r="AD1" s="3"/>
+      <c r="AE1" s="3"/>
+      <c r="AF1" s="3"/>
+      <c r="AG1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH1" s="3"/>
+      <c r="AI1" s="3"/>
+      <c r="AJ1" s="3"/>
+      <c r="AK1" s="3"/>
+      <c r="AL1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM1" s="3"/>
+      <c r="AN1" s="3"/>
+      <c r="AO1" s="3"/>
+      <c r="AP1" s="3"/>
+      <c r="AQ1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AR1" s="3"/>
+      <c r="AS1" s="3"/>
+      <c r="AT1" s="3"/>
+      <c r="AU1" s="3"/>
+      <c r="AV1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AW1" s="3"/>
+      <c r="AX1" s="3"/>
+      <c r="AY1" s="3"/>
+      <c r="AZ1" s="3"/>
+      <c r="BA1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="BB1" s="3"/>
+      <c r="BC1" s="3"/>
+      <c r="BD1" s="3"/>
+      <c r="BE1" s="3"/>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>0000000</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>POLSKA</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+    <row r="2" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AL2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AP2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AR2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AT2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AU2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AV2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AX2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AY2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AZ2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BA2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="BB2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="BC2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="BD2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BE2" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AI3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AJ3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AK3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AL3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AM3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AN3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AO3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AP3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AQ3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AR3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AS3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AT3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AU3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AV3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AW3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AX3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AY3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AZ3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="BA3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="BB3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="BC3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="BD3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="BE3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="2">
+        <f>H4+AQ4</f>
         <v>22384</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D4" s="2">
+        <f t="shared" ref="D4:G4" si="0">I4+AR4</f>
         <v>21841</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E4" s="2">
+        <f t="shared" si="0"/>
         <v>20476</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F4" s="2">
+        <f t="shared" si="0"/>
         <v>20065</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G4" s="2">
+        <f t="shared" si="0"/>
         <v>20607</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H4" s="2">
         <v>20999</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I4" s="2">
         <v>20623</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J4" s="2">
         <v>19391</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K4" s="2">
         <v>19058</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L4" s="2">
         <v>19636</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M4" s="2">
         <v>5516</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N4" s="2">
         <v>5254</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O4" s="2">
         <v>4473</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P4" s="2">
         <v>4216</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q4" s="2">
         <v>4269</v>
       </c>
-      <c r="R2" t="n">
+      <c r="R4" s="2">
         <v>5708</v>
       </c>
-      <c r="S2" t="n">
+      <c r="S4" s="2">
         <v>5566</v>
       </c>
-      <c r="T2" t="n">
+      <c r="T4" s="2">
         <v>4530</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U4" s="2">
         <v>4576</v>
       </c>
-      <c r="V2" t="n">
+      <c r="V4" s="2">
         <v>5169</v>
       </c>
-      <c r="W2" t="n">
+      <c r="W4" s="2">
         <v>1036</v>
       </c>
-      <c r="X2" t="n">
+      <c r="X4" s="2">
         <v>1012</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Y4" s="2">
         <v>925</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="Z4" s="2">
         <v>917</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AA4" s="2">
         <v>938</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AB4" s="2">
         <v>2817</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AC4" s="2">
         <v>2648</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AD4" s="2">
         <v>2835</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AE4" s="2">
         <v>3084</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AF4" s="2">
         <v>2886</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AG4" s="2">
         <v>1535</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AH4" s="2">
         <v>1607</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AI4" s="2">
         <v>1663</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AJ4" s="2">
         <v>1538</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AK4" s="2">
         <v>1505</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AL4" s="2">
         <v>4387</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AM4" s="2">
         <v>4536</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AN4" s="2">
         <v>4965</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AO4" s="2">
         <v>4727</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AP4" s="2">
         <v>4869</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AQ4" s="2">
         <v>1385</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AR4" s="2">
         <v>1218</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="AS4" s="2">
         <v>1085</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="AT4" s="2">
         <v>1007</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="AU4" s="2">
         <v>971</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AV4" s="2">
         <v>830</v>
       </c>
-      <c r="AW2" t="n">
+      <c r="AW4" s="2">
         <v>759</v>
       </c>
-      <c r="AX2" t="n">
+      <c r="AX4" s="2">
         <v>678</v>
       </c>
-      <c r="AY2" t="n">
+      <c r="AY4" s="2">
         <v>622</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="AZ4" s="2">
         <v>558</v>
       </c>
-      <c r="BA2" t="n">
+      <c r="BA4" s="2">
+        <f>AQ4-AV4</f>
         <v>555</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BB4" s="2">
         <v>459</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BC4" s="2">
         <v>407</v>
       </c>
-      <c r="BD2" t="n">
+      <c r="BD4" s="2">
         <v>385</v>
       </c>
-      <c r="BE2" t="n">
+      <c r="BE4" s="2">
         <v>413</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>0200000</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>DOLNOŚLĄSKIE</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+    <row r="5" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="2">
+        <f t="shared" ref="C5:C20" si="1">H5+AQ5</f>
         <v>1490</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D5" s="2">
+        <f t="shared" ref="D5:D20" si="2">I5+AR5</f>
         <v>1647</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E5" s="2">
+        <f t="shared" ref="E5:E20" si="3">J5+AS5</f>
         <v>1808</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F5" s="2">
+        <f t="shared" ref="F5:F20" si="4">K5+AT5</f>
         <v>1738</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G5" s="2">
+        <f t="shared" ref="G5:G20" si="5">L5+AU5</f>
         <v>1821</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H5" s="2">
         <v>1393</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I5" s="2">
         <v>1542</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J5" s="2">
         <v>1702</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K5" s="2">
         <v>1651</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L5" s="2">
         <v>1717</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M5" s="2">
         <v>375</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N5" s="2">
         <v>401</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O5" s="2">
         <v>362</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P5" s="2">
         <v>379</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q5" s="2">
         <v>401</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R5" s="2">
         <v>370</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S5" s="2">
         <v>419</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T5" s="2">
         <v>398</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U5" s="2">
         <v>387</v>
       </c>
-      <c r="V3" t="n">
+      <c r="V5" s="2">
         <v>407</v>
       </c>
-      <c r="W3" t="n">
+      <c r="W5" s="2">
         <v>60</v>
       </c>
-      <c r="X3" t="n">
+      <c r="X5" s="2">
         <v>78</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Y5" s="2">
         <v>66</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="Z5" s="2">
         <v>62</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AA5" s="2">
         <v>92</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AB5" s="2">
         <v>182</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AC5" s="2">
         <v>202</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AD5" s="2">
         <v>276</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AE5" s="2">
         <v>247</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AF5" s="2">
         <v>238</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AG5" s="2">
         <v>124</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AH5" s="2">
         <v>135</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AI5" s="2">
         <v>175</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AJ5" s="2">
         <v>189</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AK5" s="2">
         <v>173</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AL5" s="2">
         <v>282</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AM5" s="2">
         <v>307</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AN5" s="2">
         <v>425</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AO5" s="2">
         <v>387</v>
       </c>
-      <c r="AP3" t="n">
+      <c r="AP5" s="2">
         <v>406</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AQ5" s="2">
         <v>97</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AR5" s="2">
         <v>105</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="AS5" s="2">
         <v>106</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="AT5" s="2">
         <v>87</v>
       </c>
-      <c r="AU3" t="n">
+      <c r="AU5" s="2">
         <v>104</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AV5" s="2">
         <v>49</v>
       </c>
-      <c r="AW3" t="n">
+      <c r="AW5" s="2">
         <v>63</v>
       </c>
-      <c r="AX3" t="n">
+      <c r="AX5" s="2">
         <v>55</v>
       </c>
-      <c r="AY3" t="n">
+      <c r="AY5" s="2">
         <v>46</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="AZ5" s="2">
         <v>48</v>
       </c>
-      <c r="BA3" t="n">
+      <c r="BA5" s="2">
+        <f t="shared" ref="BA5:BA20" si="6">AQ5-AV5</f>
         <v>48</v>
       </c>
-      <c r="BB3" t="n">
+      <c r="BB5" s="2">
         <v>42</v>
       </c>
-      <c r="BC3" t="n">
+      <c r="BC5" s="2">
         <v>51</v>
       </c>
-      <c r="BD3" t="n">
+      <c r="BD5" s="2">
         <v>41</v>
       </c>
-      <c r="BE3" t="n">
+      <c r="BE5" s="2">
         <v>56</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>0400000</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>KUJAWSKO-POMORSKIE</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+    <row r="6" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="2">
+        <f t="shared" si="1"/>
         <v>791</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D6" s="2">
+        <f t="shared" si="2"/>
         <v>774</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E6" s="2">
+        <f t="shared" si="3"/>
         <v>744</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F6" s="2">
+        <f t="shared" si="4"/>
         <v>745</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G6" s="2">
+        <f t="shared" si="5"/>
         <v>746</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H6" s="2">
         <v>746</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I6" s="2">
         <v>727</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J6" s="2">
         <v>709</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K6" s="2">
         <v>693</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L6" s="2">
         <v>711</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M6" s="2">
         <v>205</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N6" s="2">
         <v>191</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O6" s="2">
         <v>176</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P6" s="2">
         <v>115</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q6" s="2">
         <v>142</v>
       </c>
-      <c r="R4" t="n">
+      <c r="R6" s="2">
         <v>200</v>
       </c>
-      <c r="S4" t="n">
+      <c r="S6" s="2">
         <v>195</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T6" s="2">
         <v>186</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U6" s="2">
         <v>203</v>
       </c>
-      <c r="V4" t="n">
+      <c r="V6" s="2">
         <v>222</v>
       </c>
-      <c r="W4" t="n">
+      <c r="W6" s="2">
         <v>33</v>
       </c>
-      <c r="X4" t="n">
+      <c r="X6" s="2">
         <v>40</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Y6" s="2">
         <v>35</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="Z6" s="2">
         <v>51</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AA6" s="2">
         <v>42</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AB6" s="2">
         <v>126</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AC6" s="2">
         <v>111</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AD6" s="2">
         <v>103</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AE6" s="2">
         <v>132</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AF6" s="2">
         <v>116</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AG6" s="2">
         <v>37</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AH6" s="2">
         <v>40</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AI6" s="2">
         <v>41</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AJ6" s="2">
         <v>38</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AK6" s="2">
         <v>48</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AL6" s="2">
         <v>145</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AM6" s="2">
         <v>150</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AN6" s="2">
         <v>168</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AO6" s="2">
         <v>154</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AP6" s="2">
         <v>141</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AQ6" s="2">
         <v>45</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="AR6" s="2">
         <v>47</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="AS6" s="2">
         <v>35</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="AT6" s="2">
         <v>52</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="AU6" s="2">
         <v>35</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AV6" s="2">
         <v>28</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="AW6" s="2">
         <v>29</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="AX6" s="2">
         <v>26</v>
       </c>
-      <c r="AY4" t="n">
+      <c r="AY6" s="2">
         <v>33</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="AZ6" s="2">
         <v>22</v>
       </c>
-      <c r="BA4" t="n">
+      <c r="BA6" s="2">
+        <f t="shared" si="6"/>
         <v>17</v>
       </c>
-      <c r="BB4" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC4" t="n">
+      <c r="BB6" s="2">
+        <v>18</v>
+      </c>
+      <c r="BC6" s="2">
         <v>9</v>
       </c>
-      <c r="BD4" t="n">
+      <c r="BD6" s="2">
         <v>19</v>
       </c>
-      <c r="BE4" t="n">
+      <c r="BE6" s="2">
         <v>13</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>0600000</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>LUBELSKIE</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+    <row r="7" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="2">
+        <f t="shared" si="1"/>
         <v>897</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D7" s="2">
+        <f t="shared" si="2"/>
         <v>863</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E7" s="2">
+        <f t="shared" si="3"/>
         <v>767</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F7" s="2">
+        <f t="shared" si="4"/>
         <v>763</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G7" s="2">
+        <f t="shared" si="5"/>
         <v>817</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H7" s="2">
         <v>827</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I7" s="2">
         <v>799</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J7" s="2">
         <v>716</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K7" s="2">
         <v>706</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L7" s="2">
         <v>770</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M7" s="2">
         <v>235</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N7" s="2">
         <v>225</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O7" s="2">
         <v>184</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P7" s="2">
         <v>190</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q7" s="2">
         <v>189</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R7" s="2">
         <v>203</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S7" s="2">
         <v>198</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T7" s="2">
         <v>152</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U7" s="2">
         <v>173</v>
       </c>
-      <c r="V5" t="n">
+      <c r="V7" s="2">
         <v>213</v>
       </c>
-      <c r="W5" t="n">
+      <c r="W7" s="2">
         <v>57</v>
       </c>
-      <c r="X5" t="n">
+      <c r="X7" s="2">
         <v>57</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Y7" s="2">
         <v>47</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="Z7" s="2">
         <v>47</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AA7" s="2">
         <v>43</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AB7" s="2">
         <v>106</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AC7" s="2">
         <v>113</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AD7" s="2">
         <v>93</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AE7" s="2">
         <v>101</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AF7" s="2">
         <v>106</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AG7" s="2">
         <v>41</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AH7" s="2">
         <v>44</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AI7" s="2">
         <v>43</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AJ7" s="2">
         <v>38</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AK7" s="2">
         <v>35</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AL7" s="2">
         <v>185</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AM7" s="2">
         <v>162</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AN7" s="2">
         <v>197</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AO7" s="2">
         <v>157</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="AP7" s="2">
         <v>184</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AQ7" s="2">
         <v>70</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="AR7" s="2">
         <v>64</v>
       </c>
-      <c r="AS5" t="n">
+      <c r="AS7" s="2">
         <v>51</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="AT7" s="2">
         <v>57</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="AU7" s="2">
         <v>47</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AV7" s="2">
         <v>47</v>
       </c>
-      <c r="AW5" t="n">
+      <c r="AW7" s="2">
         <v>37</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="AX7" s="2">
         <v>30</v>
       </c>
-      <c r="AY5" t="n">
+      <c r="AY7" s="2">
         <v>35</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="AZ7" s="2">
         <v>31</v>
       </c>
-      <c r="BA5" t="n">
+      <c r="BA7" s="2">
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BB7" s="2">
         <v>27</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="BC7" s="2">
         <v>21</v>
       </c>
-      <c r="BD5" t="n">
+      <c r="BD7" s="2">
         <v>22</v>
       </c>
-      <c r="BE5" t="n">
+      <c r="BE7" s="2">
         <v>16</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>0800000</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>LUBUSKIE</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
+    <row r="8" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="2">
+        <f t="shared" si="1"/>
         <v>581</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D8" s="2">
+        <f t="shared" si="2"/>
         <v>516</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E8" s="2">
+        <f t="shared" si="3"/>
         <v>483</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F8" s="2">
+        <f t="shared" si="4"/>
         <v>431</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G8" s="2">
+        <f t="shared" si="5"/>
         <v>438</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H8" s="2">
         <v>551</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I8" s="2">
         <v>497</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J8" s="2">
         <v>459</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K8" s="2">
         <v>419</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L8" s="2">
         <v>419</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M8" s="2">
         <v>176</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N8" s="2">
         <v>142</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O8" s="2">
         <v>113</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P8" s="2">
         <v>131</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q8" s="2">
         <v>122</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R8" s="2">
         <v>118</v>
       </c>
-      <c r="S6" t="n">
+      <c r="S8" s="2">
         <v>108</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T8" s="2">
         <v>87</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U8" s="2">
         <v>66</v>
       </c>
-      <c r="V6" t="n">
+      <c r="V8" s="2">
         <v>104</v>
       </c>
-      <c r="W6" t="n">
+      <c r="W8" s="2">
         <v>36</v>
       </c>
-      <c r="X6" t="n">
+      <c r="X8" s="2">
         <v>30</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Y8" s="2">
         <v>48</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="Z8" s="2">
         <v>30</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AA8" s="2">
         <v>21</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AB8" s="2">
         <v>68</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AC8" s="2">
         <v>60</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AD8" s="2">
         <v>61</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AE8" s="2">
         <v>73</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AF8" s="2">
         <v>37</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AG8" s="2">
         <v>38</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AH8" s="2">
         <v>41</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AI8" s="2">
         <v>39</v>
       </c>
-      <c r="AJ6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK6" t="n">
+      <c r="AJ8" s="2">
+        <v>18</v>
+      </c>
+      <c r="AK8" s="2">
         <v>29</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AL8" s="2">
         <v>115</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AM8" s="2">
         <v>116</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AN8" s="2">
         <v>111</v>
       </c>
-      <c r="AO6" t="n">
+      <c r="AO8" s="2">
         <v>101</v>
       </c>
-      <c r="AP6" t="n">
+      <c r="AP8" s="2">
         <v>106</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AQ8" s="2">
         <v>30</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="AR8" s="2">
         <v>19</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="AS8" s="2">
         <v>24</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="AT8" s="2">
         <v>12</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="AU8" s="2">
         <v>19</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AV8" s="2">
         <v>22</v>
       </c>
-      <c r="AW6" t="n">
+      <c r="AW8" s="2">
         <v>12</v>
       </c>
-      <c r="AX6" t="n">
+      <c r="AX8" s="2">
         <v>15</v>
       </c>
-      <c r="AY6" t="n">
+      <c r="AY8" s="2">
         <v>9</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="AZ8" s="2">
         <v>11</v>
       </c>
-      <c r="BA6" t="n">
+      <c r="BA8" s="2">
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="BB6" t="n">
+      <c r="BB8" s="2">
         <v>7</v>
       </c>
-      <c r="BC6" t="n">
+      <c r="BC8" s="2">
         <v>9</v>
       </c>
-      <c r="BD6" t="n">
+      <c r="BD8" s="2">
         <v>3</v>
       </c>
-      <c r="BE6" t="n">
+      <c r="BE8" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ŁÓDZKIE</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+    <row r="9" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="2">
+        <f t="shared" si="1"/>
         <v>2332</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D9" s="2">
+        <f t="shared" si="2"/>
         <v>2208</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E9" s="2">
+        <f t="shared" si="3"/>
         <v>2108</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F9" s="2">
+        <f t="shared" si="4"/>
         <v>2029</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G9" s="2">
+        <f t="shared" si="5"/>
         <v>2106</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H9" s="2">
         <v>2199</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I9" s="2">
         <v>2093</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J9" s="2">
         <v>1997</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K9" s="2">
         <v>1944</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L9" s="2">
         <v>2013</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M9" s="2">
         <v>576</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N9" s="2">
         <v>518</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O9" s="2">
         <v>444</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P9" s="2">
         <v>391</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q9" s="2">
         <v>394</v>
       </c>
-      <c r="R7" t="n">
+      <c r="R9" s="2">
         <v>653</v>
       </c>
-      <c r="S7" t="n">
+      <c r="S9" s="2">
         <v>577</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T9" s="2">
         <v>532</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U9" s="2">
         <v>472</v>
       </c>
-      <c r="V7" t="n">
+      <c r="V9" s="2">
         <v>549</v>
       </c>
-      <c r="W7" t="n">
+      <c r="W9" s="2">
         <v>105</v>
       </c>
-      <c r="X7" t="n">
+      <c r="X9" s="2">
         <v>87</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Y9" s="2">
         <v>63</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="Z9" s="2">
         <v>75</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AA9" s="2">
         <v>72</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AB9" s="2">
         <v>280</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AC9" s="2">
         <v>265</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AD9" s="2">
         <v>300</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AE9" s="2">
         <v>329</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AF9" s="2">
         <v>343</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AG9" s="2">
         <v>123</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AH9" s="2">
         <v>111</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AI9" s="2">
         <v>123</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AJ9" s="2">
         <v>143</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AK9" s="2">
         <v>112</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AL9" s="2">
         <v>462</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AM9" s="2">
         <v>535</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AN9" s="2">
         <v>535</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AO9" s="2">
         <v>534</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AP9" s="2">
         <v>543</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AQ9" s="2">
         <v>133</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AR9" s="2">
         <v>115</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="AS9" s="2">
         <v>111</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="AT9" s="2">
         <v>85</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="AU9" s="2">
         <v>93</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AV9" s="2">
         <v>89</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="AW9" s="2">
         <v>74</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="AX9" s="2">
         <v>72</v>
       </c>
-      <c r="AY7" t="n">
+      <c r="AY9" s="2">
         <v>49</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="AZ9" s="2">
         <v>49</v>
       </c>
-      <c r="BA7" t="n">
+      <c r="BA9" s="2">
+        <f t="shared" si="6"/>
         <v>44</v>
       </c>
-      <c r="BB7" t="n">
+      <c r="BB9" s="2">
         <v>41</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="BC9" s="2">
         <v>39</v>
       </c>
-      <c r="BD7" t="n">
+      <c r="BD9" s="2">
         <v>36</v>
       </c>
-      <c r="BE7" t="n">
+      <c r="BE9" s="2">
         <v>44</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>1200000</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>MAŁOPOLSKIE</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
+    <row r="10" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="2">
+        <f t="shared" si="1"/>
         <v>2089</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D10" s="2">
+        <f t="shared" si="2"/>
         <v>2140</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E10" s="2">
+        <f t="shared" si="3"/>
         <v>2136</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F10" s="2">
+        <f t="shared" si="4"/>
         <v>2108</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G10" s="2">
+        <f t="shared" si="5"/>
         <v>2382</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H10" s="2">
         <v>1957</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I10" s="2">
         <v>1978</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J10" s="2">
         <v>2010</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K10" s="2">
         <v>1978</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L10" s="2">
         <v>2258</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M10" s="2">
         <v>503</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N10" s="2">
         <v>518</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O10" s="2">
         <v>477</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P10" s="2">
         <v>487</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q10" s="2">
         <v>503</v>
       </c>
-      <c r="R8" t="n">
+      <c r="R10" s="2">
         <v>443</v>
       </c>
-      <c r="S8" t="n">
+      <c r="S10" s="2">
         <v>458</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T10" s="2">
         <v>421</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U10" s="2">
         <v>396</v>
       </c>
-      <c r="V8" t="n">
+      <c r="V10" s="2">
         <v>558</v>
       </c>
-      <c r="W8" t="n">
+      <c r="W10" s="2">
         <v>78</v>
       </c>
-      <c r="X8" t="n">
+      <c r="X10" s="2">
         <v>75</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Y10" s="2">
         <v>88</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="Z10" s="2">
         <v>68</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AA10" s="2">
         <v>74</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AB10" s="2">
         <v>285</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AC10" s="2">
         <v>258</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AD10" s="2">
         <v>287</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AE10" s="2">
         <v>301</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AF10" s="2">
         <v>302</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AG10" s="2">
         <v>194</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AH10" s="2">
         <v>198</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AI10" s="2">
         <v>218</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AJ10" s="2">
         <v>203</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AK10" s="2">
         <v>257</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AL10" s="2">
         <v>454</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AM10" s="2">
         <v>471</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AN10" s="2">
         <v>519</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AO10" s="2">
         <v>523</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AP10" s="2">
         <v>564</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AQ10" s="2">
         <v>132</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="AR10" s="2">
         <v>162</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="AS10" s="2">
         <v>126</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="AT10" s="2">
         <v>130</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="AU10" s="2">
         <v>124</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AV10" s="2">
         <v>72</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="AW10" s="2">
         <v>110</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="AX10" s="2">
         <v>77</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="AY10" s="2">
         <v>85</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="AZ10" s="2">
         <v>63</v>
       </c>
-      <c r="BA8" t="n">
+      <c r="BA10" s="2">
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BB10" s="2">
         <v>52</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="BC10" s="2">
         <v>49</v>
       </c>
-      <c r="BD8" t="n">
+      <c r="BD10" s="2">
         <v>45</v>
       </c>
-      <c r="BE8" t="n">
+      <c r="BE10" s="2">
         <v>61</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>1400000</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>MAZOWIECKIE</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
+    <row r="11" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="2">
+        <f t="shared" si="1"/>
         <v>2880</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D11" s="2">
+        <f t="shared" si="2"/>
         <v>2988</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E11" s="2">
+        <f t="shared" si="3"/>
         <v>2811</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" s="2">
+        <f t="shared" si="4"/>
         <v>2723</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G11" s="2">
+        <f t="shared" si="5"/>
         <v>2770</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H11" s="2">
         <v>2695</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I11" s="2">
         <v>2828</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J11" s="2">
         <v>2664</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K11" s="2">
         <v>2595</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L11" s="2">
         <v>2628</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M11" s="2">
         <v>705</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N11" s="2">
         <v>717</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O11" s="2">
         <v>613</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P11" s="2">
         <v>608</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q11" s="2">
         <v>587</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R11" s="2">
         <v>819</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S11" s="2">
         <v>765</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T11" s="2">
         <v>607</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U11" s="2">
         <v>634</v>
       </c>
-      <c r="V9" t="n">
+      <c r="V11" s="2">
         <v>706</v>
       </c>
-      <c r="W9" t="n">
+      <c r="W11" s="2">
         <v>162</v>
       </c>
-      <c r="X9" t="n">
+      <c r="X11" s="2">
         <v>134</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Y11" s="2">
         <v>168</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="Z11" s="2">
         <v>155</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AA11" s="2">
         <v>154</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AB11" s="2">
         <v>361</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AC11" s="2">
         <v>345</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AD11" s="2">
         <v>394</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AE11" s="2">
         <v>416</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AF11" s="2">
         <v>361</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AG11" s="2">
         <v>111</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AH11" s="2">
         <v>198</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AI11" s="2">
         <v>177</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AJ11" s="2">
         <v>172</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AK11" s="2">
         <v>136</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AL11" s="2">
         <v>537</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AM11" s="2">
         <v>669</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AN11" s="2">
         <v>705</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AO11" s="2">
         <v>610</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AP11" s="2">
         <v>684</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AQ11" s="2">
         <v>185</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="AR11" s="2">
         <v>160</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="AS11" s="2">
         <v>147</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="AT11" s="2">
         <v>128</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="AU11" s="2">
         <v>142</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AV11" s="2">
         <v>102</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="AW11" s="2">
         <v>86</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="AX11" s="2">
         <v>83</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="AY11" s="2">
         <v>76</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="AZ11" s="2">
         <v>74</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BA11" s="2">
+        <f t="shared" si="6"/>
         <v>83</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BB11" s="2">
         <v>74</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BC11" s="2">
         <v>64</v>
       </c>
-      <c r="BD9" t="n">
+      <c r="BD11" s="2">
         <v>52</v>
       </c>
-      <c r="BE9" t="n">
+      <c r="BE11" s="2">
         <v>68</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>1600000</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>OPOLSKIE</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
+    <row r="12" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="2">
+        <f t="shared" si="1"/>
         <v>466</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D12" s="2">
+        <f t="shared" si="2"/>
         <v>520</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E12" s="2">
+        <f t="shared" si="3"/>
         <v>427</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F12" s="2">
+        <f t="shared" si="4"/>
         <v>447</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G12" s="2">
+        <f t="shared" si="5"/>
         <v>468</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H12" s="2">
         <v>451</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I12" s="2">
         <v>504</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J12" s="2">
         <v>413</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K12" s="2">
         <v>436</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L12" s="2">
         <v>456</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M12" s="2">
         <v>89</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N12" s="2">
         <v>112</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O12" s="2">
         <v>92</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P12" s="2">
         <v>90</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q12" s="2">
         <v>93</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R12" s="2">
         <v>117</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S12" s="2">
         <v>150</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T12" s="2">
         <v>87</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U12" s="2">
         <v>113</v>
       </c>
-      <c r="V10" t="n">
+      <c r="V12" s="2">
         <v>117</v>
       </c>
-      <c r="W10" t="n">
+      <c r="W12" s="2">
         <v>25</v>
       </c>
-      <c r="X10" t="n">
+      <c r="X12" s="2">
         <v>30</v>
       </c>
-      <c r="Y10" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z10" t="n">
+      <c r="Y12" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z12" s="2">
         <v>30</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AA12" s="2">
         <v>32</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AB12" s="2">
         <v>51</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AC12" s="2">
         <v>47</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AD12" s="2">
         <v>49</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AE12" s="2">
         <v>54</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AF12" s="2">
         <v>54</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AG12" s="2">
         <v>58</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AH12" s="2">
         <v>51</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AI12" s="2">
         <v>45</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AJ12" s="2">
         <v>44</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AK12" s="2">
         <v>59</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AL12" s="2">
         <v>111</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AM12" s="2">
         <v>114</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AN12" s="2">
         <v>122</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AO12" s="2">
         <v>105</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AP12" s="2">
         <v>101</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AQ12" s="2">
         <v>15</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="AR12" s="2">
         <v>16</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="AS12" s="2">
         <v>14</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="AT12" s="2">
         <v>11</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="AU12" s="2">
         <v>12</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AV12" s="2">
         <v>8</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="AW12" s="2">
         <v>12</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="AX12" s="2">
         <v>7</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="AY12" s="2">
         <v>7</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="AZ12" s="2">
         <v>8</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BA12" s="2">
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BB12" s="2">
         <v>4</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BC12" s="2">
         <v>7</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="BD12" s="2">
         <v>4</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="BE12" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>1800000</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>PODKARPACKIE</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
+    <row r="13" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="2">
+        <f t="shared" si="1"/>
         <v>1114</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D13" s="2">
+        <f t="shared" si="2"/>
         <v>1181</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E13" s="2">
+        <f t="shared" si="3"/>
         <v>1009</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F13" s="2">
+        <f t="shared" si="4"/>
         <v>1140</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G13" s="2">
+        <f t="shared" si="5"/>
         <v>981</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H13" s="2">
         <v>1032</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I13" s="2">
         <v>1116</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J13" s="2">
         <v>952</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K13" s="2">
         <v>1078</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L13" s="2">
         <v>949</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M13" s="2">
         <v>317</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N13" s="2">
         <v>323</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O13" s="2">
         <v>256</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P13" s="2">
         <v>223</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q13" s="2">
         <v>221</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R13" s="2">
         <v>311</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S13" s="2">
         <v>313</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T13" s="2">
         <v>214</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U13" s="2">
         <v>285</v>
       </c>
-      <c r="V11" t="n">
+      <c r="V13" s="2">
         <v>231</v>
       </c>
-      <c r="W11" t="n">
+      <c r="W13" s="2">
         <v>39</v>
       </c>
-      <c r="X11" t="n">
+      <c r="X13" s="2">
         <v>56</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Y13" s="2">
         <v>35</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="Z13" s="2">
         <v>54</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AA13" s="2">
         <v>36</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AB13" s="2">
         <v>87</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AC13" s="2">
         <v>91</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AD13" s="2">
         <v>99</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AE13" s="2">
         <v>121</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AF13" s="2">
         <v>102</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AG13" s="2">
         <v>79</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AH13" s="2">
         <v>118</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AI13" s="2">
         <v>110</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AJ13" s="2">
         <v>129</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AK13" s="2">
         <v>99</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AL13" s="2">
         <v>199</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AM13" s="2">
         <v>215</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AN13" s="2">
         <v>238</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AO13" s="2">
         <v>266</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AP13" s="2">
         <v>260</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AQ13" s="2">
         <v>82</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="AR13" s="2">
         <v>65</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="AS13" s="2">
         <v>57</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="AT13" s="2">
         <v>62</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="AU13" s="2">
         <v>32</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AV13" s="2">
         <v>59</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="AW13" s="2">
         <v>46</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="AX13" s="2">
         <v>46</v>
       </c>
-      <c r="AY11" t="n">
+      <c r="AY13" s="2">
         <v>47</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="AZ13" s="2">
         <v>23</v>
       </c>
-      <c r="BA11" t="n">
+      <c r="BA13" s="2">
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
-      <c r="BB11" t="n">
+      <c r="BB13" s="2">
         <v>19</v>
       </c>
-      <c r="BC11" t="n">
+      <c r="BC13" s="2">
         <v>11</v>
       </c>
-      <c r="BD11" t="n">
+      <c r="BD13" s="2">
         <v>15</v>
       </c>
-      <c r="BE11" t="n">
+      <c r="BE13" s="2">
         <v>9</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>PODLASKIE</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
+    <row r="14" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="2">
+        <f t="shared" si="1"/>
         <v>417</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D14" s="2">
+        <f t="shared" si="2"/>
         <v>418</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E14" s="2">
+        <f t="shared" si="3"/>
         <v>321</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F14" s="2">
+        <f t="shared" si="4"/>
         <v>329</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G14" s="2">
+        <f t="shared" si="5"/>
         <v>338</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H14" s="2">
         <v>393</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I14" s="2">
         <v>400</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J14" s="2">
         <v>310</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K14" s="2">
         <v>314</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L14" s="2">
         <v>325</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M14" s="2">
         <v>117</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N14" s="2">
         <v>95</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O14" s="2">
         <v>79</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P14" s="2">
         <v>68</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q14" s="2">
         <v>72</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R14" s="2">
         <v>102</v>
       </c>
-      <c r="S12" t="n">
+      <c r="S14" s="2">
         <v>121</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T14" s="2">
         <v>65</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U14" s="2">
         <v>87</v>
       </c>
-      <c r="V12" t="n">
+      <c r="V14" s="2">
         <v>94</v>
       </c>
-      <c r="W12" t="n">
+      <c r="W14" s="2">
         <v>17</v>
       </c>
-      <c r="X12" t="n">
+      <c r="X14" s="2">
         <v>25</v>
       </c>
-      <c r="Y12" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z12" t="n">
+      <c r="Y14" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z14" s="2">
         <v>21</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AA14" s="2">
         <v>23</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AB14" s="2">
         <v>56</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AC14" s="2">
         <v>54</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AD14" s="2">
         <v>49</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AE14" s="2">
         <v>56</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AF14" s="2">
         <v>49</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AG14" s="2">
         <v>20</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AH14" s="2">
         <v>20</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AI14" s="2">
         <v>22</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AJ14" s="2">
         <v>9</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AK14" s="2">
         <v>14</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AL14" s="2">
         <v>81</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AM14" s="2">
         <v>85</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AN14" s="2">
         <v>77</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AO14" s="2">
         <v>73</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AP14" s="2">
         <v>73</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AQ14" s="2">
         <v>24</v>
       </c>
-      <c r="AR12" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS12" t="n">
+      <c r="AR14" s="2">
+        <v>18</v>
+      </c>
+      <c r="AS14" s="2">
         <v>11</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="AT14" s="2">
         <v>15</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="AU14" s="2">
         <v>13</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AV14" s="2">
         <v>16</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="AW14" s="2">
         <v>9</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="AX14" s="2">
         <v>5</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="AY14" s="2">
         <v>6</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="AZ14" s="2">
         <v>9</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BA14" s="2">
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BB14" s="2">
         <v>9</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BC14" s="2">
         <v>6</v>
       </c>
-      <c r="BD12" t="n">
+      <c r="BD14" s="2">
         <v>9</v>
       </c>
-      <c r="BE12" t="n">
+      <c r="BE14" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2200000</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>POMORSKIE</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
+    <row r="15" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="2">
+        <f t="shared" si="1"/>
         <v>1748</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D15" s="2">
+        <f t="shared" si="2"/>
         <v>1699</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E15" s="2">
+        <f t="shared" si="3"/>
         <v>1523</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F15" s="2">
+        <f t="shared" si="4"/>
         <v>1492</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G15" s="2">
+        <f t="shared" si="5"/>
         <v>1618</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H15" s="2">
         <v>1639</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I15" s="2">
         <v>1623</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J15" s="2">
         <v>1461</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K15" s="2">
         <v>1435</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L15" s="2">
         <v>1554</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M15" s="2">
         <v>474</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N15" s="2">
         <v>449</v>
       </c>
-      <c r="O13" t="n">
+      <c r="O15" s="2">
         <v>353</v>
       </c>
-      <c r="P13" t="n">
+      <c r="P15" s="2">
         <v>345</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="Q15" s="2">
         <v>379</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R15" s="2">
         <v>419</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S15" s="2">
         <v>431</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T15" s="2">
         <v>308</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U15" s="2">
         <v>343</v>
       </c>
-      <c r="V13" t="n">
+      <c r="V15" s="2">
         <v>388</v>
       </c>
-      <c r="W13" t="n">
+      <c r="W15" s="2">
         <v>86</v>
       </c>
-      <c r="X13" t="n">
+      <c r="X15" s="2">
         <v>80</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="Y15" s="2">
         <v>47</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="Z15" s="2">
         <v>58</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AA15" s="2">
         <v>88</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AB15" s="2">
         <v>220</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AC15" s="2">
         <v>237</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AD15" s="2">
         <v>228</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AE15" s="2">
         <v>246</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AF15" s="2">
         <v>215</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AG15" s="2">
         <v>112</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AH15" s="2">
         <v>104</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AI15" s="2">
         <v>123</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AJ15" s="2">
         <v>99</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AK15" s="2">
         <v>107</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AL15" s="2">
         <v>328</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AM15" s="2">
         <v>322</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AN15" s="2">
         <v>402</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AO15" s="2">
         <v>344</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AP15" s="2">
         <v>377</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AQ15" s="2">
         <v>109</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="AR15" s="2">
         <v>76</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="AS15" s="2">
         <v>62</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="AT15" s="2">
         <v>57</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="AU15" s="2">
         <v>64</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="AV15" s="2">
         <v>72</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="AW15" s="2">
         <v>51</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="AX15" s="2">
         <v>45</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="AY15" s="2">
         <v>39</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="AZ15" s="2">
         <v>40</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BA15" s="2">
+        <f t="shared" si="6"/>
         <v>37</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BB15" s="2">
         <v>25</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BC15" s="2">
         <v>17</v>
       </c>
-      <c r="BD13" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE13" t="n">
+      <c r="BD15" s="2">
+        <v>18</v>
+      </c>
+      <c r="BE15" s="2">
         <v>24</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2400000</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>ŚLĄSKIE</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
+    <row r="16" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="2">
+        <f t="shared" si="1"/>
         <v>2265</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D16" s="2">
+        <f t="shared" si="2"/>
         <v>2127</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E16" s="2">
+        <f t="shared" si="3"/>
         <v>1922</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F16" s="2">
+        <f t="shared" si="4"/>
         <v>1818</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G16" s="2">
+        <f t="shared" si="5"/>
         <v>1712</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H16" s="2">
         <v>2087</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I16" s="2">
         <v>1989</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J16" s="2">
         <v>1810</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K16" s="2">
         <v>1704</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L16" s="2">
         <v>1628</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M16" s="2">
         <v>371</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N16" s="2">
         <v>329</v>
       </c>
-      <c r="O14" t="n">
+      <c r="O16" s="2">
         <v>260</v>
       </c>
-      <c r="P14" t="n">
+      <c r="P16" s="2">
         <v>205</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="Q16" s="2">
         <v>165</v>
       </c>
-      <c r="R14" t="n">
+      <c r="R16" s="2">
         <v>584</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S16" s="2">
         <v>612</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T16" s="2">
         <v>463</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U16" s="2">
         <v>457</v>
       </c>
-      <c r="V14" t="n">
+      <c r="V16" s="2">
         <v>474</v>
       </c>
-      <c r="W14" t="n">
+      <c r="W16" s="2">
         <v>80</v>
       </c>
-      <c r="X14" t="n">
+      <c r="X16" s="2">
         <v>90</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="Y16" s="2">
         <v>70</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="Z16" s="2">
         <v>70</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AA16" s="2">
         <v>66</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AB16" s="2">
         <v>372</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AC16" s="2">
         <v>292</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AD16" s="2">
         <v>339</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AE16" s="2">
         <v>360</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AF16" s="2">
         <v>331</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AG16" s="2">
         <v>216</v>
       </c>
-      <c r="AH14" t="n">
+      <c r="AH16" s="2">
         <v>215</v>
       </c>
-      <c r="AI14" t="n">
+      <c r="AI16" s="2">
         <v>211</v>
       </c>
-      <c r="AJ14" t="n">
+      <c r="AJ16" s="2">
         <v>170</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AK16" s="2">
         <v>167</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AL16" s="2">
         <v>464</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AM16" s="2">
         <v>451</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="AN16" s="2">
         <v>467</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="AO16" s="2">
         <v>442</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="AP16" s="2">
         <v>425</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="AQ16" s="2">
         <v>178</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="AR16" s="2">
         <v>138</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="AS16" s="2">
         <v>112</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="AT16" s="2">
         <v>114</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="AU16" s="2">
         <v>84</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="AV16" s="2">
         <v>116</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="AW16" s="2">
         <v>91</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="AX16" s="2">
         <v>74</v>
       </c>
-      <c r="AY14" t="n">
+      <c r="AY16" s="2">
         <v>77</v>
       </c>
-      <c r="AZ14" t="n">
+      <c r="AZ16" s="2">
         <v>57</v>
       </c>
-      <c r="BA14" t="n">
+      <c r="BA16" s="2">
+        <f t="shared" si="6"/>
         <v>62</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="BB16" s="2">
         <v>47</v>
       </c>
-      <c r="BC14" t="n">
+      <c r="BC16" s="2">
         <v>38</v>
       </c>
-      <c r="BD14" t="n">
+      <c r="BD16" s="2">
         <v>37</v>
       </c>
-      <c r="BE14" t="n">
+      <c r="BE16" s="2">
         <v>27</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2600000</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ŚWIĘTOKRZYSKIE</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
+    <row r="17" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="2">
+        <f t="shared" si="1"/>
         <v>772</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D17" s="2">
+        <f t="shared" si="2"/>
         <v>715</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E17" s="2">
+        <f t="shared" si="3"/>
         <v>591</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F17" s="2">
+        <f t="shared" si="4"/>
         <v>623</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G17" s="2">
+        <f t="shared" si="5"/>
         <v>618</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H17" s="2">
         <v>720</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I17" s="2">
         <v>672</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J17" s="2">
         <v>553</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K17" s="2">
         <v>581</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L17" s="2">
         <v>587</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M17" s="2">
         <v>212</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N17" s="2">
         <v>171</v>
       </c>
-      <c r="O15" t="n">
+      <c r="O17" s="2">
         <v>124</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P17" s="2">
         <v>122</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q17" s="2">
         <v>113</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R17" s="2">
         <v>167</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S17" s="2">
         <v>176</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T17" s="2">
         <v>132</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U17" s="2">
         <v>161</v>
       </c>
-      <c r="V15" t="n">
+      <c r="V17" s="2">
         <v>175</v>
       </c>
-      <c r="W15" t="n">
+      <c r="W17" s="2">
         <v>37</v>
       </c>
-      <c r="X15" t="n">
+      <c r="X17" s="2">
         <v>35</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="Y17" s="2">
         <v>36</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="Z17" s="2">
         <v>33</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AA17" s="2">
         <v>28</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AB17" s="2">
         <v>81</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AC17" s="2">
         <v>88</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AD17" s="2">
         <v>76</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AE17" s="2">
         <v>87</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AF17" s="2">
         <v>88</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AG17" s="2">
         <v>69</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AH17" s="2">
         <v>59</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AI17" s="2">
         <v>60</v>
       </c>
-      <c r="AJ15" t="n">
+      <c r="AJ17" s="2">
         <v>56</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AK17" s="2">
         <v>54</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AL17" s="2">
         <v>154</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AM17" s="2">
         <v>143</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AN17" s="2">
         <v>125</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="AO17" s="2">
         <v>122</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AP17" s="2">
         <v>129</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AQ17" s="2">
         <v>52</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="AR17" s="2">
         <v>43</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="AS17" s="2">
         <v>38</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="AT17" s="2">
         <v>42</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="AU17" s="2">
         <v>31</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="AV17" s="2">
         <v>29</v>
       </c>
-      <c r="AW15" t="n">
+      <c r="AW17" s="2">
         <v>27</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="AX17" s="2">
         <v>23</v>
       </c>
-      <c r="AY15" t="n">
+      <c r="AY17" s="2">
         <v>24</v>
       </c>
-      <c r="AZ15" t="n">
+      <c r="AZ17" s="2">
         <v>21</v>
       </c>
-      <c r="BA15" t="n">
+      <c r="BA17" s="2">
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="BB17" s="2">
         <v>16</v>
       </c>
-      <c r="BC15" t="n">
+      <c r="BC17" s="2">
         <v>15</v>
       </c>
-      <c r="BD15" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE15" t="n">
+      <c r="BD17" s="2">
+        <v>18</v>
+      </c>
+      <c r="BE17" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2800000</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>WARMIŃSKO-MAZURSKIE</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
+    <row r="18" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="2">
+        <f t="shared" si="1"/>
         <v>962</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D18" s="2">
+        <f t="shared" si="2"/>
         <v>854</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E18" s="2">
+        <f t="shared" si="3"/>
         <v>771</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F18" s="2">
+        <f t="shared" si="4"/>
         <v>694</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G18" s="2">
+        <f t="shared" si="5"/>
         <v>709</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H18" s="2">
         <v>912</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I18" s="2">
         <v>818</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J18" s="2">
         <v>725</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K18" s="2">
         <v>672</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L18" s="2">
         <v>683</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M18" s="2">
         <v>324</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N18" s="2">
         <v>305</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O18" s="2">
         <v>265</v>
       </c>
-      <c r="P16" t="n">
+      <c r="P18" s="2">
         <v>216</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="Q18" s="2">
         <v>209</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R18" s="2">
         <v>178</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S18" s="2">
         <v>153</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T18" s="2">
         <v>133</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U18" s="2">
         <v>112</v>
       </c>
-      <c r="V16" t="n">
+      <c r="V18" s="2">
         <v>139</v>
       </c>
-      <c r="W16" t="n">
+      <c r="W18" s="2">
         <v>48</v>
       </c>
-      <c r="X16" t="n">
+      <c r="X18" s="2">
         <v>49</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="Y18" s="2">
         <v>37</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="Z18" s="2">
         <v>33</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AA18" s="2">
         <v>35</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AB18" s="2">
         <v>107</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AC18" s="2">
         <v>91</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AD18" s="2">
         <v>91</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AE18" s="2">
         <v>98</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AF18" s="2">
         <v>106</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AG18" s="2">
         <v>68</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AH18" s="2">
         <v>43</v>
       </c>
-      <c r="AI16" t="n">
+      <c r="AI18" s="2">
         <v>41</v>
       </c>
-      <c r="AJ16" t="n">
+      <c r="AJ18" s="2">
         <v>44</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AK18" s="2">
         <v>29</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AL18" s="2">
         <v>187</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AM18" s="2">
         <v>177</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="AN18" s="2">
         <v>158</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="AO18" s="2">
         <v>169</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AP18" s="2">
         <v>165</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AQ18" s="2">
         <v>50</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="AR18" s="2">
         <v>36</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="AS18" s="2">
         <v>46</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="AT18" s="2">
         <v>22</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="AU18" s="2">
         <v>26</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="AV18" s="2">
         <v>33</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="AW18" s="2">
         <v>25</v>
       </c>
-      <c r="AX16" t="n">
+      <c r="AX18" s="2">
         <v>32</v>
       </c>
-      <c r="AY16" t="n">
+      <c r="AY18" s="2">
         <v>12</v>
       </c>
-      <c r="AZ16" t="n">
+      <c r="AZ18" s="2">
         <v>14</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="BA18" s="2">
+        <f t="shared" si="6"/>
         <v>17</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BB18" s="2">
         <v>11</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BC18" s="2">
         <v>14</v>
       </c>
-      <c r="BD16" t="n">
+      <c r="BD18" s="2">
         <v>10</v>
       </c>
-      <c r="BE16" t="n">
+      <c r="BE18" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>3000000</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>WIELKOPOLSKIE</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
+    <row r="19" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="2">
+        <f t="shared" si="1"/>
         <v>2723</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D19" s="2">
+        <f t="shared" si="2"/>
         <v>2317</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E19" s="2">
+        <f t="shared" si="3"/>
         <v>2224</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F19" s="2">
+        <f t="shared" si="4"/>
         <v>2248</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G19" s="2">
+        <f t="shared" si="5"/>
         <v>2380</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H19" s="2">
         <v>2596</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I19" s="2">
         <v>2205</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J19" s="2">
         <v>2126</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K19" s="2">
         <v>2152</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L19" s="2">
         <v>2270</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M19" s="2">
         <v>631</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N19" s="2">
         <v>554</v>
       </c>
-      <c r="O17" t="n">
+      <c r="O19" s="2">
         <v>513</v>
       </c>
-      <c r="P17" t="n">
+      <c r="P19" s="2">
         <v>492</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="Q19" s="2">
         <v>536</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R19" s="2">
         <v>820</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S19" s="2">
         <v>673</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T19" s="2">
         <v>564</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U19" s="2">
         <v>543</v>
       </c>
-      <c r="V17" t="n">
+      <c r="V19" s="2">
         <v>624</v>
       </c>
-      <c r="W17" t="n">
+      <c r="W19" s="2">
         <v>142</v>
       </c>
-      <c r="X17" t="n">
+      <c r="X19" s="2">
         <v>106</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="Y19" s="2">
         <v>116</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="Z19" s="2">
         <v>101</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AA19" s="2">
         <v>104</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AB19" s="2">
         <v>294</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AC19" s="2">
         <v>258</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AD19" s="2">
         <v>253</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AE19" s="2">
         <v>336</v>
       </c>
-      <c r="AF17" t="n">
+      <c r="AF19" s="2">
         <v>309</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AG19" s="2">
         <v>166</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AH19" s="2">
         <v>169</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AI19" s="2">
         <v>163</v>
       </c>
-      <c r="AJ17" t="n">
+      <c r="AJ19" s="2">
         <v>131</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AK19" s="2">
         <v>133</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AL19" s="2">
         <v>543</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="AM19" s="2">
         <v>445</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="AN19" s="2">
         <v>517</v>
       </c>
-      <c r="AO17" t="n">
+      <c r="AO19" s="2">
         <v>549</v>
       </c>
-      <c r="AP17" t="n">
+      <c r="AP19" s="2">
         <v>564</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AQ19" s="2">
         <v>127</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="AR19" s="2">
         <v>112</v>
       </c>
-      <c r="AS17" t="n">
+      <c r="AS19" s="2">
         <v>98</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="AT19" s="2">
         <v>96</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="AU19" s="2">
         <v>110</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="AV19" s="2">
         <v>61</v>
       </c>
-      <c r="AW17" t="n">
+      <c r="AW19" s="2">
         <v>58</v>
       </c>
-      <c r="AX17" t="n">
+      <c r="AX19" s="2">
         <v>54</v>
       </c>
-      <c r="AY17" t="n">
+      <c r="AY19" s="2">
         <v>55</v>
       </c>
-      <c r="AZ17" t="n">
+      <c r="AZ19" s="2">
         <v>69</v>
       </c>
-      <c r="BA17" t="n">
+      <c r="BA19" s="2">
+        <f t="shared" si="6"/>
         <v>66</v>
       </c>
-      <c r="BB17" t="n">
+      <c r="BB19" s="2">
         <v>54</v>
       </c>
-      <c r="BC17" t="n">
+      <c r="BC19" s="2">
         <v>44</v>
       </c>
-      <c r="BD17" t="n">
+      <c r="BD19" s="2">
         <v>41</v>
       </c>
-      <c r="BE17" t="n">
+      <c r="BE19" s="2">
         <v>41</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>3200000</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ZACHODNIOPOMORSKIE</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
+    <row r="20" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="2">
+        <f t="shared" si="1"/>
         <v>857</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D20" s="2">
+        <f t="shared" si="2"/>
         <v>874</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E20" s="2">
+        <f t="shared" si="3"/>
         <v>831</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F20" s="2">
+        <f t="shared" si="4"/>
         <v>737</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G20" s="2">
+        <f t="shared" si="5"/>
         <v>703</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H20" s="2">
         <v>801</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I20" s="2">
         <v>832</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J20" s="2">
         <v>784</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K20" s="2">
         <v>700</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L20" s="2">
         <v>668</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M20" s="2">
         <v>206</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N20" s="2">
         <v>204</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O20" s="2">
         <v>162</v>
       </c>
-      <c r="P18" t="n">
+      <c r="P20" s="2">
         <v>154</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Q20" s="2">
         <v>143</v>
       </c>
-      <c r="R18" t="n">
+      <c r="R20" s="2">
         <v>204</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S20" s="2">
         <v>217</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T20" s="2">
         <v>181</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U20" s="2">
         <v>144</v>
       </c>
-      <c r="V18" t="n">
+      <c r="V20" s="2">
         <v>168</v>
       </c>
-      <c r="W18" t="n">
+      <c r="W20" s="2">
         <v>31</v>
       </c>
-      <c r="X18" t="n">
+      <c r="X20" s="2">
         <v>40</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Y20" s="2">
         <v>33</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="Z20" s="2">
         <v>29</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AA20" s="2">
         <v>28</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AB20" s="2">
         <v>141</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AC20" s="2">
         <v>136</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AD20" s="2">
         <v>137</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AE20" s="2">
         <v>127</v>
       </c>
-      <c r="AF18" t="n">
+      <c r="AF20" s="2">
         <v>129</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AG20" s="2">
         <v>79</v>
       </c>
-      <c r="AH18" t="n">
+      <c r="AH20" s="2">
         <v>61</v>
       </c>
-      <c r="AI18" t="n">
+      <c r="AI20" s="2">
         <v>72</v>
       </c>
-      <c r="AJ18" t="n">
+      <c r="AJ20" s="2">
         <v>55</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AK20" s="2">
         <v>53</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AL20" s="2">
         <v>140</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="AM20" s="2">
         <v>174</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="AN20" s="2">
         <v>199</v>
       </c>
-      <c r="AO18" t="n">
+      <c r="AO20" s="2">
         <v>191</v>
       </c>
-      <c r="AP18" t="n">
+      <c r="AP20" s="2">
         <v>147</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AQ20" s="2">
         <v>56</v>
       </c>
-      <c r="AR18" t="n">
+      <c r="AR20" s="2">
         <v>42</v>
       </c>
-      <c r="AS18" t="n">
+      <c r="AS20" s="2">
         <v>47</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="AT20" s="2">
         <v>37</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="AU20" s="2">
         <v>35</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="AV20" s="2">
         <v>27</v>
       </c>
-      <c r="AW18" t="n">
+      <c r="AW20" s="2">
         <v>29</v>
       </c>
-      <c r="AX18" t="n">
+      <c r="AX20" s="2">
         <v>34</v>
       </c>
-      <c r="AY18" t="n">
+      <c r="AY20" s="2">
         <v>22</v>
       </c>
-      <c r="AZ18" t="n">
+      <c r="AZ20" s="2">
         <v>19</v>
       </c>
-      <c r="BA18" t="n">
+      <c r="BA20" s="2">
+        <f t="shared" si="6"/>
         <v>29</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BB20" s="2">
         <v>13</v>
       </c>
-      <c r="BC18" t="n">
+      <c r="BC20" s="2">
         <v>13</v>
       </c>
-      <c r="BD18" t="n">
+      <c r="BD20" s="2">
         <v>15</v>
       </c>
-      <c r="BE18" t="n">
+      <c r="BE20" s="2">
         <v>16</v>
       </c>
+    </row>
+    <row r="22" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="C22" s="2"/>
+      <c r="F22" s="2"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="H1:L1"/>
+    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="AQ1:AU1"/>
+    <mergeCell ref="AV1:AZ1"/>
+    <mergeCell ref="BA1:BE1"/>
+    <mergeCell ref="R1:V1"/>
+    <mergeCell ref="W1:AA1"/>
+    <mergeCell ref="AB1:AF1"/>
+    <mergeCell ref="AG1:AK1"/>
+    <mergeCell ref="AL1:AP1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/dane.xlsx
+++ b/dane.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/dane.xlsx
+++ b/dane.xlsx
@@ -425,291 +425,286 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE18"/>
+  <dimension ref="A1:BD18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kod</t>
+          <t>Nazwa</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Nazwa</t>
+          <t>ogółem_2020</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ogółem_2020</t>
+          <t>ogółem_2021</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>ogółem_2021</t>
+          <t>ogółem_2022</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ogółem_2022</t>
+          <t>ogółem_2023</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ogółem_2023</t>
+          <t>ogółem_2024</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>ogółem_2024</t>
+          <t>wina kierujących pojazdami - ogółem_2020</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - ogółem_2020</t>
+          <t>wina kierujących pojazdami - ogółem_2021</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - ogółem_2021</t>
+          <t>wina kierujących pojazdami - ogółem_2022</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - ogółem_2022</t>
+          <t>wina kierujących pojazdami - ogółem_2023</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - ogółem_2023</t>
+          <t>wina kierujących pojazdami - ogółem_2024</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - ogółem_2024</t>
+          <t>wina kierujących pojazdami - niedostosowanie prędkości do warunków ruchu_2020</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - niedostosowanie prędkości do warunków ruchu_2020</t>
+          <t>wina kierujących pojazdami - niedostosowanie prędkości do warunków ruchu_2021</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - niedostosowanie prędkości do warunków ruchu_2021</t>
+          <t>wina kierujących pojazdami - niedostosowanie prędkości do warunków ruchu_2022</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - niedostosowanie prędkości do warunków ruchu_2022</t>
+          <t>wina kierujących pojazdami - niedostosowanie prędkości do warunków ruchu_2023</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - niedostosowanie prędkości do warunków ruchu_2023</t>
+          <t>wina kierujących pojazdami - niedostosowanie prędkości do warunków ruchu_2024</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - niedostosowanie prędkości do warunków ruchu_2024</t>
+          <t>wina kierujących pojazdami - nieprzestrzeganie pierwszeństwa przejazdu_2020</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - nieprzestrzeganie pierwszeństwa przejazdu_2020</t>
+          <t>wina kierujących pojazdami - nieprzestrzeganie pierwszeństwa przejazdu_2021</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - nieprzestrzeganie pierwszeństwa przejazdu_2021</t>
+          <t>wina kierujących pojazdami - nieprzestrzeganie pierwszeństwa przejazdu_2022</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - nieprzestrzeganie pierwszeństwa przejazdu_2022</t>
+          <t>wina kierujących pojazdami - nieprzestrzeganie pierwszeństwa przejazdu_2023</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - nieprzestrzeganie pierwszeństwa przejazdu_2023</t>
+          <t>wina kierujących pojazdami - nieprzestrzeganie pierwszeństwa przejazdu_2024</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - nieprzestrzeganie pierwszeństwa przejazdu_2024</t>
+          <t>wina kierujących pojazdami - nieprawidłowe wyprzedzanie_2020</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - nieprawidłowe wyprzedzanie_2020</t>
+          <t>wina kierujących pojazdami - nieprawidłowe wyprzedzanie_2021</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - nieprawidłowe wyprzedzanie_2021</t>
+          <t>wina kierujących pojazdami - nieprawidłowe wyprzedzanie_2022</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - nieprawidłowe wyprzedzanie_2022</t>
+          <t>wina kierujących pojazdami - nieprawidłowe wyprzedzanie_2023</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - nieprawidłowe wyprzedzanie_2023</t>
+          <t>wina kierujących pojazdami - nieprawidłowe wyprzedzanie_2024</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - nieprawidłowe wyprzedzanie_2024</t>
+          <t>wina kierujących pojazdami - nieprawidłowe zachowanie wobec pieszych_2020</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - nieprawidłowe zachowanie wobec pieszych_2020</t>
+          <t>wina kierujących pojazdami - nieprawidłowe zachowanie wobec pieszych_2021</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - nieprawidłowe zachowanie wobec pieszych_2021</t>
+          <t>wina kierujących pojazdami - nieprawidłowe zachowanie wobec pieszych_2022</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - nieprawidłowe zachowanie wobec pieszych_2022</t>
+          <t>wina kierujących pojazdami - nieprawidłowe zachowanie wobec pieszych_2023</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - nieprawidłowe zachowanie wobec pieszych_2023</t>
+          <t>wina kierujących pojazdami - nieprawidłowe zachowanie wobec pieszych_2024</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - nieprawidłowe zachowanie wobec pieszych_2024</t>
+          <t>wina kierujących pojazdami - niezachowanie bezpiecznej odległości między pojazdami_2020</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - niezachowanie bezpiecznej odległości między pojazdami_2020</t>
+          <t>wina kierujących pojazdami - niezachowanie bezpiecznej odległości między pojazdami_2021</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - niezachowanie bezpiecznej odległości między pojazdami_2021</t>
+          <t>wina kierujących pojazdami - niezachowanie bezpiecznej odległości między pojazdami_2022</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - niezachowanie bezpiecznej odległości między pojazdami_2022</t>
+          <t>wina kierujących pojazdami - niezachowanie bezpiecznej odległości między pojazdami_2023</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - niezachowanie bezpiecznej odległości między pojazdami_2023</t>
+          <t>wina kierujących pojazdami - niezachowanie bezpiecznej odległości między pojazdami_2024</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - niezachowanie bezpiecznej odległości między pojazdami_2024</t>
+          <t>wina kierujących pojazdami - pozostałe_2020</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - pozostałe_2020</t>
+          <t>wina kierujących pojazdami - pozostałe_2021</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - pozostałe_2021</t>
+          <t>wina kierujących pojazdami - pozostałe_2022</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - pozostałe_2022</t>
+          <t>wina kierujących pojazdami - pozostałe_2023</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - pozostałe_2023</t>
+          <t>wina kierujących pojazdami - pozostałe_2024</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>wina kierujących pojazdami - pozostałe_2024</t>
+          <t>wina pieszych - ogółem_2020</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>wina pieszych - ogółem_2020</t>
+          <t>wina pieszych - ogółem_2021</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>wina pieszych - ogółem_2021</t>
+          <t>wina pieszych - ogółem_2022</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>wina pieszych - ogółem_2022</t>
+          <t>wina pieszych - ogółem_2023</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>wina pieszych - ogółem_2023</t>
+          <t>wina pieszych - ogółem_2024</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>wina pieszych - ogółem_2024</t>
+          <t>wina pieszych - nieostrożne wejście na jezdnię_2020</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>wina pieszych - nieostrożne wejście na jezdnię_2020</t>
+          <t>wina pieszych - nieostrożne wejście na jezdnię_2021</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>wina pieszych - nieostrożne wejście na jezdnię_2021</t>
+          <t>wina pieszych - nieostrożne wejście na jezdnię_2022</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>wina pieszych - nieostrożne wejście na jezdnię_2022</t>
+          <t>wina pieszych - nieostrożne wejście na jezdnię_2023</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>wina pieszych - nieostrożne wejście na jezdnię_2023</t>
+          <t>wina pieszych - nieostrożne wejście na jezdnię_2024</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>wina pieszych - nieostrożne wejście na jezdnię_2024</t>
+          <t>wina pieszych - pozostałe_2020</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>wina pieszych - pozostałe_2020</t>
+          <t>wina pieszych - pozostałe_2021</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>wina pieszych - pozostałe_2021</t>
+          <t>wina pieszych - pozostałe_2022</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>wina pieszych - pozostałe_2022</t>
+          <t>wina pieszych - pozostałe_2023</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>wina pieszych - pozostałe_2023</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>wina pieszych - pozostałe_2024</t>
         </is>
@@ -718,3009 +713,2924 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0000000</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
           <t>POLSKA</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>22384</v>
+      </c>
       <c r="C2" t="n">
-        <v>22384</v>
+        <v>21841</v>
       </c>
       <c r="D2" t="n">
-        <v>21841</v>
+        <v>20476</v>
       </c>
       <c r="E2" t="n">
-        <v>20476</v>
+        <v>20065</v>
       </c>
       <c r="F2" t="n">
-        <v>20065</v>
+        <v>20607</v>
       </c>
       <c r="G2" t="n">
-        <v>20607</v>
+        <v>20999</v>
       </c>
       <c r="H2" t="n">
-        <v>20999</v>
+        <v>20623</v>
       </c>
       <c r="I2" t="n">
-        <v>20623</v>
+        <v>19391</v>
       </c>
       <c r="J2" t="n">
-        <v>19391</v>
+        <v>19058</v>
       </c>
       <c r="K2" t="n">
-        <v>19058</v>
+        <v>19636</v>
       </c>
       <c r="L2" t="n">
-        <v>19636</v>
+        <v>5516</v>
       </c>
       <c r="M2" t="n">
-        <v>5516</v>
+        <v>5254</v>
       </c>
       <c r="N2" t="n">
-        <v>5254</v>
+        <v>4473</v>
       </c>
       <c r="O2" t="n">
-        <v>4473</v>
+        <v>4216</v>
       </c>
       <c r="P2" t="n">
-        <v>4216</v>
+        <v>4269</v>
       </c>
       <c r="Q2" t="n">
-        <v>4269</v>
+        <v>5708</v>
       </c>
       <c r="R2" t="n">
-        <v>5708</v>
+        <v>5566</v>
       </c>
       <c r="S2" t="n">
-        <v>5566</v>
+        <v>4530</v>
       </c>
       <c r="T2" t="n">
-        <v>4530</v>
+        <v>4576</v>
       </c>
       <c r="U2" t="n">
-        <v>4576</v>
+        <v>5169</v>
       </c>
       <c r="V2" t="n">
-        <v>5169</v>
+        <v>1036</v>
       </c>
       <c r="W2" t="n">
-        <v>1036</v>
+        <v>1012</v>
       </c>
       <c r="X2" t="n">
-        <v>1012</v>
+        <v>925</v>
       </c>
       <c r="Y2" t="n">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="Z2" t="n">
-        <v>917</v>
+        <v>938</v>
       </c>
       <c r="AA2" t="n">
-        <v>938</v>
+        <v>2817</v>
       </c>
       <c r="AB2" t="n">
-        <v>2817</v>
+        <v>2648</v>
       </c>
       <c r="AC2" t="n">
-        <v>2648</v>
+        <v>2835</v>
       </c>
       <c r="AD2" t="n">
-        <v>2835</v>
+        <v>3084</v>
       </c>
       <c r="AE2" t="n">
-        <v>3084</v>
+        <v>2886</v>
       </c>
       <c r="AF2" t="n">
-        <v>2886</v>
+        <v>1535</v>
       </c>
       <c r="AG2" t="n">
-        <v>1535</v>
+        <v>1607</v>
       </c>
       <c r="AH2" t="n">
-        <v>1607</v>
+        <v>1663</v>
       </c>
       <c r="AI2" t="n">
-        <v>1663</v>
+        <v>1538</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1538</v>
+        <v>1505</v>
       </c>
       <c r="AK2" t="n">
-        <v>1505</v>
+        <v>4387</v>
       </c>
       <c r="AL2" t="n">
-        <v>4387</v>
+        <v>4536</v>
       </c>
       <c r="AM2" t="n">
-        <v>4536</v>
+        <v>4965</v>
       </c>
       <c r="AN2" t="n">
-        <v>4965</v>
+        <v>4727</v>
       </c>
       <c r="AO2" t="n">
-        <v>4727</v>
+        <v>4869</v>
       </c>
       <c r="AP2" t="n">
-        <v>4869</v>
+        <v>1385</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1385</v>
+        <v>1218</v>
       </c>
       <c r="AR2" t="n">
-        <v>1218</v>
+        <v>1085</v>
       </c>
       <c r="AS2" t="n">
-        <v>1085</v>
+        <v>1007</v>
       </c>
       <c r="AT2" t="n">
-        <v>1007</v>
+        <v>971</v>
       </c>
       <c r="AU2" t="n">
-        <v>971</v>
+        <v>830</v>
       </c>
       <c r="AV2" t="n">
-        <v>830</v>
+        <v>759</v>
       </c>
       <c r="AW2" t="n">
-        <v>759</v>
+        <v>678</v>
       </c>
       <c r="AX2" t="n">
-        <v>678</v>
+        <v>622</v>
       </c>
       <c r="AY2" t="n">
-        <v>622</v>
+        <v>558</v>
       </c>
       <c r="AZ2" t="n">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="BA2" t="n">
-        <v>555</v>
+        <v>459</v>
       </c>
       <c r="BB2" t="n">
-        <v>459</v>
+        <v>407</v>
       </c>
       <c r="BC2" t="n">
-        <v>407</v>
+        <v>385</v>
       </c>
       <c r="BD2" t="n">
-        <v>385</v>
-      </c>
-      <c r="BE2" t="n">
         <v>413</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0200000</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
           <t>DOLNOŚLĄSKIE</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>1490</v>
+      </c>
       <c r="C3" t="n">
-        <v>1490</v>
+        <v>1647</v>
       </c>
       <c r="D3" t="n">
-        <v>1647</v>
+        <v>1808</v>
       </c>
       <c r="E3" t="n">
-        <v>1808</v>
+        <v>1738</v>
       </c>
       <c r="F3" t="n">
-        <v>1738</v>
+        <v>1821</v>
       </c>
       <c r="G3" t="n">
-        <v>1821</v>
+        <v>1393</v>
       </c>
       <c r="H3" t="n">
-        <v>1393</v>
+        <v>1542</v>
       </c>
       <c r="I3" t="n">
-        <v>1542</v>
+        <v>1702</v>
       </c>
       <c r="J3" t="n">
-        <v>1702</v>
+        <v>1651</v>
       </c>
       <c r="K3" t="n">
-        <v>1651</v>
+        <v>1717</v>
       </c>
       <c r="L3" t="n">
-        <v>1717</v>
+        <v>375</v>
       </c>
       <c r="M3" t="n">
-        <v>375</v>
+        <v>401</v>
       </c>
       <c r="N3" t="n">
+        <v>362</v>
+      </c>
+      <c r="O3" t="n">
+        <v>379</v>
+      </c>
+      <c r="P3" t="n">
         <v>401</v>
       </c>
-      <c r="O3" t="n">
-        <v>362</v>
-      </c>
-      <c r="P3" t="n">
-        <v>379</v>
-      </c>
       <c r="Q3" t="n">
-        <v>401</v>
+        <v>370</v>
       </c>
       <c r="R3" t="n">
-        <v>370</v>
+        <v>419</v>
       </c>
       <c r="S3" t="n">
-        <v>419</v>
+        <v>398</v>
       </c>
       <c r="T3" t="n">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="U3" t="n">
+        <v>407</v>
+      </c>
+      <c r="V3" t="n">
+        <v>60</v>
+      </c>
+      <c r="W3" t="n">
+        <v>78</v>
+      </c>
+      <c r="X3" t="n">
+        <v>66</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>62</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>92</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>182</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>202</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>276</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>247</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>238</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>124</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>135</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>175</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>189</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>173</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>282</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>307</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>425</v>
+      </c>
+      <c r="AN3" t="n">
         <v>387</v>
       </c>
-      <c r="V3" t="n">
-        <v>407</v>
-      </c>
-      <c r="W3" t="n">
-        <v>60</v>
-      </c>
-      <c r="X3" t="n">
-        <v>78</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>66</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>62</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>92</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>182</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>202</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>276</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>247</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>238</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>124</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>135</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>175</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>189</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>173</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>282</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>307</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>425</v>
-      </c>
       <c r="AO3" t="n">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="AP3" t="n">
-        <v>406</v>
+        <v>97</v>
       </c>
       <c r="AQ3" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="AR3" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AS3" t="n">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="AT3" t="n">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="AU3" t="n">
-        <v>104</v>
+        <v>49</v>
       </c>
       <c r="AV3" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="AW3" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="AX3" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AY3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AZ3" t="n">
         <v>48</v>
       </c>
       <c r="BA3" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="BB3" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="BC3" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="BD3" t="n">
-        <v>41</v>
-      </c>
-      <c r="BE3" t="n">
         <v>56</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0400000</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
           <t>KUJAWSKO-POMORSKIE</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>791</v>
+      </c>
       <c r="C4" t="n">
-        <v>791</v>
+        <v>774</v>
       </c>
       <c r="D4" t="n">
-        <v>774</v>
+        <v>744</v>
       </c>
       <c r="E4" t="n">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="F4" t="n">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="G4" t="n">
         <v>746</v>
       </c>
       <c r="H4" t="n">
-        <v>746</v>
+        <v>727</v>
       </c>
       <c r="I4" t="n">
-        <v>727</v>
+        <v>709</v>
       </c>
       <c r="J4" t="n">
-        <v>709</v>
+        <v>693</v>
       </c>
       <c r="K4" t="n">
-        <v>693</v>
+        <v>711</v>
       </c>
       <c r="L4" t="n">
-        <v>711</v>
+        <v>205</v>
       </c>
       <c r="M4" t="n">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="N4" t="n">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="O4" t="n">
-        <v>176</v>
+        <v>115</v>
       </c>
       <c r="P4" t="n">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="Q4" t="n">
-        <v>142</v>
+        <v>200</v>
       </c>
       <c r="R4" t="n">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="S4" t="n">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="T4" t="n">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="U4" t="n">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="V4" t="n">
-        <v>222</v>
+        <v>33</v>
       </c>
       <c r="W4" t="n">
+        <v>40</v>
+      </c>
+      <c r="X4" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>126</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>111</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>103</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>132</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>116</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>37</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>41</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>145</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>168</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>154</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>141</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>45</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>47</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>35</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>52</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>35</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX4" t="n">
         <v>33</v>
       </c>
-      <c r="X4" t="n">
-        <v>40</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>51</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>126</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>111</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>103</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>132</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>116</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>37</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>41</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>145</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>168</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>154</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>141</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>45</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>47</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>35</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>52</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>35</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>26</v>
-      </c>
       <c r="AY4" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="AZ4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BA4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB4" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="BC4" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="BD4" t="n">
-        <v>19</v>
-      </c>
-      <c r="BE4" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0600000</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
           <t>LUBELSKIE</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>897</v>
+      </c>
       <c r="C5" t="n">
-        <v>897</v>
+        <v>863</v>
       </c>
       <c r="D5" t="n">
-        <v>863</v>
+        <v>767</v>
       </c>
       <c r="E5" t="n">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="F5" t="n">
-        <v>763</v>
+        <v>817</v>
       </c>
       <c r="G5" t="n">
-        <v>817</v>
+        <v>827</v>
       </c>
       <c r="H5" t="n">
-        <v>827</v>
+        <v>799</v>
       </c>
       <c r="I5" t="n">
-        <v>799</v>
+        <v>716</v>
       </c>
       <c r="J5" t="n">
-        <v>716</v>
+        <v>706</v>
       </c>
       <c r="K5" t="n">
-        <v>706</v>
+        <v>770</v>
       </c>
       <c r="L5" t="n">
-        <v>770</v>
+        <v>235</v>
       </c>
       <c r="M5" t="n">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="N5" t="n">
-        <v>225</v>
+        <v>184</v>
       </c>
       <c r="O5" t="n">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="P5" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q5" t="n">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="R5" t="n">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="S5" t="n">
-        <v>198</v>
+        <v>152</v>
       </c>
       <c r="T5" t="n">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="U5" t="n">
-        <v>173</v>
+        <v>213</v>
       </c>
       <c r="V5" t="n">
-        <v>213</v>
+        <v>57</v>
       </c>
       <c r="W5" t="n">
         <v>57</v>
       </c>
       <c r="X5" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="Y5" t="n">
         <v>47</v>
       </c>
       <c r="Z5" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>106</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>113</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>93</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>101</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>106</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>41</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>43</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>35</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>185</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>162</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>197</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>157</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>184</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>64</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>51</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>57</v>
+      </c>
+      <c r="AT5" t="n">
         <v>47</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>43</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>106</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>113</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>93</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>101</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>106</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>41</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>44</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>43</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>35</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>185</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>162</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>197</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>157</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>184</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>70</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>64</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>51</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>57</v>
       </c>
       <c r="AU5" t="n">
         <v>47</v>
       </c>
       <c r="AV5" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="AW5" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="AX5" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="AY5" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AZ5" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="BA5" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BB5" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="BC5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD5" t="n">
-        <v>22</v>
-      </c>
-      <c r="BE5" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0800000</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
           <t>LUBUSKIE</t>
         </is>
       </c>
+      <c r="B6" t="n">
+        <v>581</v>
+      </c>
       <c r="C6" t="n">
-        <v>581</v>
+        <v>516</v>
       </c>
       <c r="D6" t="n">
-        <v>516</v>
+        <v>483</v>
       </c>
       <c r="E6" t="n">
-        <v>483</v>
+        <v>431</v>
       </c>
       <c r="F6" t="n">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="G6" t="n">
-        <v>438</v>
+        <v>551</v>
       </c>
       <c r="H6" t="n">
-        <v>551</v>
+        <v>497</v>
       </c>
       <c r="I6" t="n">
-        <v>497</v>
+        <v>459</v>
       </c>
       <c r="J6" t="n">
-        <v>459</v>
+        <v>419</v>
       </c>
       <c r="K6" t="n">
         <v>419</v>
       </c>
       <c r="L6" t="n">
-        <v>419</v>
+        <v>176</v>
       </c>
       <c r="M6" t="n">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="N6" t="n">
-        <v>142</v>
+        <v>113</v>
       </c>
       <c r="O6" t="n">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="P6" t="n">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="Q6" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="R6" t="n">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="S6" t="n">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="T6" t="n">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="U6" t="n">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="V6" t="n">
-        <v>104</v>
+        <v>36</v>
       </c>
       <c r="W6" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="X6" t="n">
+        <v>48</v>
+      </c>
+      <c r="Y6" t="n">
         <v>30</v>
       </c>
-      <c r="Y6" t="n">
-        <v>48</v>
-      </c>
       <c r="Z6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>68</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>61</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>73</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>37</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>41</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>39</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>116</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>111</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>101</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>106</v>
+      </c>
+      <c r="AP6" t="n">
         <v>30</v>
       </c>
-      <c r="AA6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>68</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>61</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>73</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>37</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>41</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>39</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>115</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>116</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>111</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>101</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>106</v>
-      </c>
       <c r="AQ6" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="AR6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT6" t="n">
         <v>19</v>
       </c>
-      <c r="AS6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AT6" t="n">
+      <c r="AU6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AV6" t="n">
         <v>12</v>
       </c>
-      <c r="AU6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>22</v>
-      </c>
       <c r="AW6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AX6" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AY6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB6" t="n">
         <v>9</v>
       </c>
-      <c r="AZ6" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>7</v>
-      </c>
       <c r="BC6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="BD6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE6" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1000000</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
           <t>ŁÓDZKIE</t>
         </is>
       </c>
+      <c r="B7" t="n">
+        <v>2332</v>
+      </c>
       <c r="C7" t="n">
-        <v>2332</v>
+        <v>2208</v>
       </c>
       <c r="D7" t="n">
-        <v>2208</v>
+        <v>2108</v>
       </c>
       <c r="E7" t="n">
-        <v>2108</v>
+        <v>2029</v>
       </c>
       <c r="F7" t="n">
-        <v>2029</v>
+        <v>2106</v>
       </c>
       <c r="G7" t="n">
-        <v>2106</v>
+        <v>2199</v>
       </c>
       <c r="H7" t="n">
-        <v>2199</v>
+        <v>2093</v>
       </c>
       <c r="I7" t="n">
-        <v>2093</v>
+        <v>1997</v>
       </c>
       <c r="J7" t="n">
-        <v>1997</v>
+        <v>1944</v>
       </c>
       <c r="K7" t="n">
-        <v>1944</v>
+        <v>2013</v>
       </c>
       <c r="L7" t="n">
-        <v>2013</v>
+        <v>576</v>
       </c>
       <c r="M7" t="n">
-        <v>576</v>
+        <v>518</v>
       </c>
       <c r="N7" t="n">
-        <v>518</v>
+        <v>444</v>
       </c>
       <c r="O7" t="n">
-        <v>444</v>
+        <v>391</v>
       </c>
       <c r="P7" t="n">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="Q7" t="n">
-        <v>394</v>
+        <v>653</v>
       </c>
       <c r="R7" t="n">
-        <v>653</v>
+        <v>577</v>
       </c>
       <c r="S7" t="n">
-        <v>577</v>
+        <v>532</v>
       </c>
       <c r="T7" t="n">
-        <v>532</v>
+        <v>472</v>
       </c>
       <c r="U7" t="n">
-        <v>472</v>
+        <v>549</v>
       </c>
       <c r="V7" t="n">
-        <v>549</v>
+        <v>105</v>
       </c>
       <c r="W7" t="n">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="X7" t="n">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="Y7" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="Z7" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="AA7" t="n">
-        <v>72</v>
+        <v>280</v>
       </c>
       <c r="AB7" t="n">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="AC7" t="n">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="AD7" t="n">
-        <v>300</v>
+        <v>329</v>
       </c>
       <c r="AE7" t="n">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="AF7" t="n">
-        <v>343</v>
+        <v>123</v>
       </c>
       <c r="AG7" t="n">
+        <v>111</v>
+      </c>
+      <c r="AH7" t="n">
         <v>123</v>
       </c>
-      <c r="AH7" t="n">
-        <v>111</v>
-      </c>
       <c r="AI7" t="n">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="AJ7" t="n">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="AK7" t="n">
-        <v>112</v>
+        <v>462</v>
       </c>
       <c r="AL7" t="n">
-        <v>462</v>
+        <v>535</v>
       </c>
       <c r="AM7" t="n">
         <v>535</v>
       </c>
       <c r="AN7" t="n">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AO7" t="n">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="AP7" t="n">
-        <v>543</v>
+        <v>133</v>
       </c>
       <c r="AQ7" t="n">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="AR7" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AS7" t="n">
-        <v>111</v>
+        <v>85</v>
       </c>
       <c r="AT7" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="AU7" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AV7" t="n">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="AW7" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AX7" t="n">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="AY7" t="n">
         <v>49</v>
       </c>
       <c r="AZ7" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="BA7" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="BB7" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="BC7" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="BD7" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE7" t="n">
         <v>44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1200000</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
           <t>MAŁOPOLSKIE</t>
         </is>
       </c>
+      <c r="B8" t="n">
+        <v>2089</v>
+      </c>
       <c r="C8" t="n">
-        <v>2089</v>
+        <v>2140</v>
       </c>
       <c r="D8" t="n">
-        <v>2140</v>
+        <v>2136</v>
       </c>
       <c r="E8" t="n">
-        <v>2136</v>
+        <v>2108</v>
       </c>
       <c r="F8" t="n">
-        <v>2108</v>
+        <v>2382</v>
       </c>
       <c r="G8" t="n">
-        <v>2382</v>
+        <v>1957</v>
       </c>
       <c r="H8" t="n">
-        <v>1957</v>
+        <v>1978</v>
       </c>
       <c r="I8" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J8" t="n">
         <v>1978</v>
       </c>
-      <c r="J8" t="n">
-        <v>2010</v>
-      </c>
       <c r="K8" t="n">
-        <v>1978</v>
+        <v>2258</v>
       </c>
       <c r="L8" t="n">
-        <v>2258</v>
+        <v>503</v>
       </c>
       <c r="M8" t="n">
+        <v>518</v>
+      </c>
+      <c r="N8" t="n">
+        <v>477</v>
+      </c>
+      <c r="O8" t="n">
+        <v>487</v>
+      </c>
+      <c r="P8" t="n">
         <v>503</v>
       </c>
-      <c r="N8" t="n">
-        <v>518</v>
-      </c>
-      <c r="O8" t="n">
-        <v>477</v>
-      </c>
-      <c r="P8" t="n">
-        <v>487</v>
-      </c>
       <c r="Q8" t="n">
-        <v>503</v>
+        <v>443</v>
       </c>
       <c r="R8" t="n">
-        <v>443</v>
+        <v>458</v>
       </c>
       <c r="S8" t="n">
-        <v>458</v>
+        <v>421</v>
       </c>
       <c r="T8" t="n">
-        <v>421</v>
+        <v>396</v>
       </c>
       <c r="U8" t="n">
-        <v>396</v>
+        <v>558</v>
       </c>
       <c r="V8" t="n">
-        <v>558</v>
+        <v>78</v>
       </c>
       <c r="W8" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="X8" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="Y8" t="n">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="Z8" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="AA8" t="n">
-        <v>74</v>
+        <v>285</v>
       </c>
       <c r="AB8" t="n">
-        <v>285</v>
+        <v>258</v>
       </c>
       <c r="AC8" t="n">
-        <v>258</v>
+        <v>287</v>
       </c>
       <c r="AD8" t="n">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="AE8" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AF8" t="n">
-        <v>302</v>
+        <v>194</v>
       </c>
       <c r="AG8" t="n">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="AH8" t="n">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="AI8" t="n">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="AJ8" t="n">
-        <v>203</v>
+        <v>257</v>
       </c>
       <c r="AK8" t="n">
-        <v>257</v>
+        <v>454</v>
       </c>
       <c r="AL8" t="n">
-        <v>454</v>
+        <v>471</v>
       </c>
       <c r="AM8" t="n">
-        <v>471</v>
+        <v>519</v>
       </c>
       <c r="AN8" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="AO8" t="n">
-        <v>523</v>
+        <v>564</v>
       </c>
       <c r="AP8" t="n">
-        <v>564</v>
+        <v>132</v>
       </c>
       <c r="AQ8" t="n">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="AR8" t="n">
-        <v>162</v>
+        <v>126</v>
       </c>
       <c r="AS8" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AT8" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="AU8" t="n">
-        <v>124</v>
+        <v>72</v>
       </c>
       <c r="AV8" t="n">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="AW8" t="n">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="AX8" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AY8" t="n">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="AZ8" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="BA8" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="BB8" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="BC8" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="BD8" t="n">
-        <v>45</v>
-      </c>
-      <c r="BE8" t="n">
         <v>61</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1400000</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
           <t>MAZOWIECKIE</t>
         </is>
       </c>
+      <c r="B9" t="n">
+        <v>2880</v>
+      </c>
       <c r="C9" t="n">
-        <v>2880</v>
+        <v>2988</v>
       </c>
       <c r="D9" t="n">
-        <v>2988</v>
+        <v>2811</v>
       </c>
       <c r="E9" t="n">
-        <v>2811</v>
+        <v>2723</v>
       </c>
       <c r="F9" t="n">
-        <v>2723</v>
+        <v>2770</v>
       </c>
       <c r="G9" t="n">
-        <v>2770</v>
+        <v>2695</v>
       </c>
       <c r="H9" t="n">
-        <v>2695</v>
+        <v>2828</v>
       </c>
       <c r="I9" t="n">
-        <v>2828</v>
+        <v>2664</v>
       </c>
       <c r="J9" t="n">
-        <v>2664</v>
+        <v>2595</v>
       </c>
       <c r="K9" t="n">
-        <v>2595</v>
+        <v>2628</v>
       </c>
       <c r="L9" t="n">
-        <v>2628</v>
+        <v>705</v>
       </c>
       <c r="M9" t="n">
+        <v>717</v>
+      </c>
+      <c r="N9" t="n">
+        <v>613</v>
+      </c>
+      <c r="O9" t="n">
+        <v>608</v>
+      </c>
+      <c r="P9" t="n">
+        <v>587</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>819</v>
+      </c>
+      <c r="R9" t="n">
+        <v>765</v>
+      </c>
+      <c r="S9" t="n">
+        <v>607</v>
+      </c>
+      <c r="T9" t="n">
+        <v>634</v>
+      </c>
+      <c r="U9" t="n">
+        <v>706</v>
+      </c>
+      <c r="V9" t="n">
+        <v>162</v>
+      </c>
+      <c r="W9" t="n">
+        <v>134</v>
+      </c>
+      <c r="X9" t="n">
+        <v>168</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>155</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>154</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>361</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>345</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>394</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>416</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>361</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>111</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>198</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>177</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>172</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>136</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>537</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>669</v>
+      </c>
+      <c r="AM9" t="n">
         <v>705</v>
       </c>
-      <c r="N9" t="n">
-        <v>717</v>
-      </c>
-      <c r="O9" t="n">
-        <v>613</v>
-      </c>
-      <c r="P9" t="n">
-        <v>608</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>587</v>
-      </c>
-      <c r="R9" t="n">
-        <v>819</v>
-      </c>
-      <c r="S9" t="n">
-        <v>765</v>
-      </c>
-      <c r="T9" t="n">
-        <v>607</v>
-      </c>
-      <c r="U9" t="n">
-        <v>634</v>
-      </c>
-      <c r="V9" t="n">
-        <v>706</v>
-      </c>
-      <c r="W9" t="n">
-        <v>162</v>
-      </c>
-      <c r="X9" t="n">
-        <v>134</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>168</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>155</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>154</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>361</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>345</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>394</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>416</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>361</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>111</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>198</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>177</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>172</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>136</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>537</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>669</v>
-      </c>
       <c r="AN9" t="n">
-        <v>705</v>
+        <v>610</v>
       </c>
       <c r="AO9" t="n">
-        <v>610</v>
+        <v>684</v>
       </c>
       <c r="AP9" t="n">
-        <v>684</v>
+        <v>185</v>
       </c>
       <c r="AQ9" t="n">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="AR9" t="n">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="AS9" t="n">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="AT9" t="n">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="AU9" t="n">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="AV9" t="n">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="AW9" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="AX9" t="n">
+        <v>76</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>74</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>83</v>
       </c>
-      <c r="AY9" t="n">
-        <v>76</v>
-      </c>
-      <c r="AZ9" t="n">
+      <c r="BA9" t="n">
         <v>74</v>
       </c>
-      <c r="BA9" t="n">
-        <v>83</v>
-      </c>
       <c r="BB9" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="BC9" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="BD9" t="n">
-        <v>52</v>
-      </c>
-      <c r="BE9" t="n">
         <v>68</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1600000</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
           <t>OPOLSKIE</t>
         </is>
       </c>
+      <c r="B10" t="n">
+        <v>466</v>
+      </c>
       <c r="C10" t="n">
-        <v>466</v>
+        <v>520</v>
       </c>
       <c r="D10" t="n">
-        <v>520</v>
+        <v>427</v>
       </c>
       <c r="E10" t="n">
-        <v>427</v>
+        <v>447</v>
       </c>
       <c r="F10" t="n">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="G10" t="n">
-        <v>468</v>
+        <v>451</v>
       </c>
       <c r="H10" t="n">
-        <v>451</v>
+        <v>504</v>
       </c>
       <c r="I10" t="n">
-        <v>504</v>
+        <v>413</v>
       </c>
       <c r="J10" t="n">
-        <v>413</v>
+        <v>436</v>
       </c>
       <c r="K10" t="n">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="L10" t="n">
-        <v>456</v>
+        <v>89</v>
       </c>
       <c r="M10" t="n">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="N10" t="n">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="O10" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="P10" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Q10" t="n">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="R10" t="n">
+        <v>150</v>
+      </c>
+      <c r="S10" t="n">
+        <v>87</v>
+      </c>
+      <c r="T10" t="n">
+        <v>113</v>
+      </c>
+      <c r="U10" t="n">
         <v>117</v>
       </c>
-      <c r="S10" t="n">
-        <v>150</v>
-      </c>
-      <c r="T10" t="n">
-        <v>87</v>
-      </c>
-      <c r="U10" t="n">
-        <v>113</v>
-      </c>
       <c r="V10" t="n">
-        <v>117</v>
+        <v>25</v>
       </c>
       <c r="W10" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="X10" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y10" t="n">
         <v>30</v>
       </c>
-      <c r="Y10" t="n">
-        <v>18</v>
-      </c>
       <c r="Z10" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA10" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="AB10" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="AC10" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AD10" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="AE10" t="n">
         <v>54</v>
       </c>
       <c r="AF10" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="AG10" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="AH10" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="AI10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AJ10" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="AK10" t="n">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="AL10" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="AM10" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="AN10" t="n">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AO10" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="AP10" t="n">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="AQ10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AS10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AT10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV10" t="n">
         <v>12</v>
       </c>
-      <c r="AV10" t="n">
-        <v>8</v>
-      </c>
       <c r="AW10" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AX10" t="n">
         <v>7</v>
       </c>
       <c r="AY10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>7</v>
       </c>
-      <c r="AZ10" t="n">
-        <v>8</v>
-      </c>
       <c r="BA10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB10" t="n">
         <v>7</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BC10" t="n">
         <v>4</v>
       </c>
-      <c r="BC10" t="n">
-        <v>7</v>
-      </c>
       <c r="BD10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE10" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1800000</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
           <t>PODKARPACKIE</t>
         </is>
       </c>
+      <c r="B11" t="n">
+        <v>1114</v>
+      </c>
       <c r="C11" t="n">
-        <v>1114</v>
+        <v>1181</v>
       </c>
       <c r="D11" t="n">
-        <v>1181</v>
+        <v>1009</v>
       </c>
       <c r="E11" t="n">
-        <v>1009</v>
+        <v>1140</v>
       </c>
       <c r="F11" t="n">
-        <v>1140</v>
+        <v>981</v>
       </c>
       <c r="G11" t="n">
-        <v>981</v>
+        <v>1032</v>
       </c>
       <c r="H11" t="n">
-        <v>1032</v>
+        <v>1116</v>
       </c>
       <c r="I11" t="n">
-        <v>1116</v>
+        <v>952</v>
       </c>
       <c r="J11" t="n">
-        <v>952</v>
+        <v>1078</v>
       </c>
       <c r="K11" t="n">
-        <v>1078</v>
+        <v>949</v>
       </c>
       <c r="L11" t="n">
-        <v>949</v>
+        <v>317</v>
       </c>
       <c r="M11" t="n">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="N11" t="n">
-        <v>323</v>
+        <v>256</v>
       </c>
       <c r="O11" t="n">
-        <v>256</v>
+        <v>223</v>
       </c>
       <c r="P11" t="n">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="Q11" t="n">
-        <v>221</v>
+        <v>311</v>
       </c>
       <c r="R11" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="S11" t="n">
-        <v>313</v>
+        <v>214</v>
       </c>
       <c r="T11" t="n">
-        <v>214</v>
+        <v>285</v>
       </c>
       <c r="U11" t="n">
-        <v>285</v>
+        <v>231</v>
       </c>
       <c r="V11" t="n">
-        <v>231</v>
+        <v>39</v>
       </c>
       <c r="W11" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="X11" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="Y11" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="Z11" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="AA11" t="n">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="AB11" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="AC11" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="AD11" t="n">
+        <v>121</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>102</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>79</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>118</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>129</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>99</v>
       </c>
-      <c r="AE11" t="n">
-        <v>121</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>102</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>79</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>118</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>129</v>
-      </c>
       <c r="AK11" t="n">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="AL11" t="n">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="AM11" t="n">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="AN11" t="n">
-        <v>238</v>
+        <v>266</v>
       </c>
       <c r="AO11" t="n">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="AP11" t="n">
-        <v>260</v>
+        <v>82</v>
       </c>
       <c r="AQ11" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="AR11" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="AS11" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="AT11" t="n">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="AU11" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="AV11" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="AW11" t="n">
         <v>46</v>
       </c>
       <c r="AX11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AY11" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="AZ11" t="n">
         <v>23</v>
       </c>
       <c r="BA11" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BB11" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="BC11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BD11" t="n">
-        <v>15</v>
-      </c>
-      <c r="BE11" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2000000</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
           <t>PODLASKIE</t>
         </is>
       </c>
+      <c r="B12" t="n">
+        <v>417</v>
+      </c>
       <c r="C12" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D12" t="n">
-        <v>418</v>
+        <v>321</v>
       </c>
       <c r="E12" t="n">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="F12" t="n">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="G12" t="n">
-        <v>338</v>
+        <v>393</v>
       </c>
       <c r="H12" t="n">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="I12" t="n">
-        <v>400</v>
+        <v>310</v>
       </c>
       <c r="J12" t="n">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="K12" t="n">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="L12" t="n">
-        <v>325</v>
+        <v>117</v>
       </c>
       <c r="M12" t="n">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="N12" t="n">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="O12" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="P12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="Q12" t="n">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="R12" t="n">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="S12" t="n">
-        <v>121</v>
+        <v>65</v>
       </c>
       <c r="T12" t="n">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="U12" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="V12" t="n">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="W12" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="X12" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="Y12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Z12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AA12" t="n">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="AB12" t="n">
+        <v>54</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>49</v>
+      </c>
+      <c r="AD12" t="n">
         <v>56</v>
       </c>
-      <c r="AC12" t="n">
-        <v>54</v>
-      </c>
-      <c r="AD12" t="n">
+      <c r="AE12" t="n">
         <v>49</v>
       </c>
-      <c r="AE12" t="n">
-        <v>56</v>
-      </c>
       <c r="AF12" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="AG12" t="n">
         <v>20</v>
       </c>
       <c r="AH12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI12" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="AJ12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AK12" t="n">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="AL12" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="AM12" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AN12" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="AO12" t="n">
         <v>73</v>
       </c>
       <c r="AP12" t="n">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="AQ12" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AR12" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AS12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AT12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AU12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AV12" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AW12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY12" t="n">
         <v>9</v>
       </c>
-      <c r="AX12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY12" t="n">
+      <c r="AZ12" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB12" t="n">
         <v>6</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BC12" t="n">
         <v>9</v>
       </c>
-      <c r="BA12" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>6</v>
-      </c>
       <c r="BD12" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE12" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2200000</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
           <t>POMORSKIE</t>
         </is>
       </c>
+      <c r="B13" t="n">
+        <v>1748</v>
+      </c>
       <c r="C13" t="n">
-        <v>1748</v>
+        <v>1699</v>
       </c>
       <c r="D13" t="n">
-        <v>1699</v>
+        <v>1523</v>
       </c>
       <c r="E13" t="n">
-        <v>1523</v>
+        <v>1492</v>
       </c>
       <c r="F13" t="n">
-        <v>1492</v>
+        <v>1618</v>
       </c>
       <c r="G13" t="n">
-        <v>1618</v>
+        <v>1639</v>
       </c>
       <c r="H13" t="n">
-        <v>1639</v>
+        <v>1623</v>
       </c>
       <c r="I13" t="n">
-        <v>1623</v>
+        <v>1461</v>
       </c>
       <c r="J13" t="n">
-        <v>1461</v>
+        <v>1435</v>
       </c>
       <c r="K13" t="n">
-        <v>1435</v>
+        <v>1554</v>
       </c>
       <c r="L13" t="n">
-        <v>1554</v>
+        <v>474</v>
       </c>
       <c r="M13" t="n">
-        <v>474</v>
+        <v>449</v>
       </c>
       <c r="N13" t="n">
-        <v>449</v>
+        <v>353</v>
       </c>
       <c r="O13" t="n">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="P13" t="n">
-        <v>345</v>
+        <v>379</v>
       </c>
       <c r="Q13" t="n">
-        <v>379</v>
+        <v>419</v>
       </c>
       <c r="R13" t="n">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="S13" t="n">
-        <v>431</v>
+        <v>308</v>
       </c>
       <c r="T13" t="n">
-        <v>308</v>
+        <v>343</v>
       </c>
       <c r="U13" t="n">
-        <v>343</v>
+        <v>388</v>
       </c>
       <c r="V13" t="n">
-        <v>388</v>
+        <v>86</v>
       </c>
       <c r="W13" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="X13" t="n">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="Y13" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="Z13" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="AA13" t="n">
-        <v>88</v>
+        <v>220</v>
       </c>
       <c r="AB13" t="n">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="AC13" t="n">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="AD13" t="n">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="AE13" t="n">
-        <v>246</v>
+        <v>215</v>
       </c>
       <c r="AF13" t="n">
-        <v>215</v>
+        <v>112</v>
       </c>
       <c r="AG13" t="n">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="AH13" t="n">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="AI13" t="n">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="AJ13" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="AK13" t="n">
-        <v>107</v>
+        <v>328</v>
       </c>
       <c r="AL13" t="n">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="AM13" t="n">
-        <v>322</v>
+        <v>402</v>
       </c>
       <c r="AN13" t="n">
-        <v>402</v>
+        <v>344</v>
       </c>
       <c r="AO13" t="n">
-        <v>344</v>
+        <v>377</v>
       </c>
       <c r="AP13" t="n">
-        <v>377</v>
+        <v>109</v>
       </c>
       <c r="AQ13" t="n">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="AR13" t="n">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="AS13" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="AT13" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="AU13" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="AV13" t="n">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="AW13" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="AX13" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="AY13" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AZ13" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="BA13" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="BB13" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="BC13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD13" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE13" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2400000</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
           <t>ŚLĄSKIE</t>
         </is>
       </c>
+      <c r="B14" t="n">
+        <v>2265</v>
+      </c>
       <c r="C14" t="n">
-        <v>2265</v>
+        <v>2127</v>
       </c>
       <c r="D14" t="n">
-        <v>2127</v>
+        <v>1922</v>
       </c>
       <c r="E14" t="n">
-        <v>1922</v>
+        <v>1818</v>
       </c>
       <c r="F14" t="n">
-        <v>1818</v>
+        <v>1712</v>
       </c>
       <c r="G14" t="n">
-        <v>1712</v>
+        <v>2087</v>
       </c>
       <c r="H14" t="n">
-        <v>2087</v>
+        <v>1989</v>
       </c>
       <c r="I14" t="n">
-        <v>1989</v>
+        <v>1810</v>
       </c>
       <c r="J14" t="n">
-        <v>1810</v>
+        <v>1704</v>
       </c>
       <c r="K14" t="n">
-        <v>1704</v>
+        <v>1628</v>
       </c>
       <c r="L14" t="n">
-        <v>1628</v>
+        <v>371</v>
       </c>
       <c r="M14" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
       <c r="N14" t="n">
-        <v>329</v>
+        <v>260</v>
       </c>
       <c r="O14" t="n">
-        <v>260</v>
+        <v>205</v>
       </c>
       <c r="P14" t="n">
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="Q14" t="n">
-        <v>165</v>
+        <v>584</v>
       </c>
       <c r="R14" t="n">
-        <v>584</v>
+        <v>612</v>
       </c>
       <c r="S14" t="n">
-        <v>612</v>
+        <v>463</v>
       </c>
       <c r="T14" t="n">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="U14" t="n">
-        <v>457</v>
+        <v>474</v>
       </c>
       <c r="V14" t="n">
-        <v>474</v>
+        <v>80</v>
       </c>
       <c r="W14" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="X14" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="Y14" t="n">
         <v>70</v>
       </c>
       <c r="Z14" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="AA14" t="n">
-        <v>66</v>
+        <v>372</v>
       </c>
       <c r="AB14" t="n">
-        <v>372</v>
+        <v>292</v>
       </c>
       <c r="AC14" t="n">
-        <v>292</v>
+        <v>339</v>
       </c>
       <c r="AD14" t="n">
-        <v>339</v>
+        <v>360</v>
       </c>
       <c r="AE14" t="n">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="AF14" t="n">
-        <v>331</v>
+        <v>216</v>
       </c>
       <c r="AG14" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AH14" t="n">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="AI14" t="n">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="AJ14" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="AK14" t="n">
-        <v>167</v>
+        <v>464</v>
       </c>
       <c r="AL14" t="n">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="AM14" t="n">
-        <v>451</v>
+        <v>467</v>
       </c>
       <c r="AN14" t="n">
-        <v>467</v>
+        <v>442</v>
       </c>
       <c r="AO14" t="n">
-        <v>442</v>
+        <v>425</v>
       </c>
       <c r="AP14" t="n">
-        <v>425</v>
+        <v>178</v>
       </c>
       <c r="AQ14" t="n">
-        <v>178</v>
+        <v>138</v>
       </c>
       <c r="AR14" t="n">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="AS14" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AT14" t="n">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="AU14" t="n">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="AV14" t="n">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="AW14" t="n">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="AX14" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AY14" t="n">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="AZ14" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="BA14" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="BB14" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="BC14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="BD14" t="n">
-        <v>37</v>
-      </c>
-      <c r="BE14" t="n">
         <v>27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2600000</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
           <t>ŚWIĘTOKRZYSKIE</t>
         </is>
       </c>
+      <c r="B15" t="n">
+        <v>772</v>
+      </c>
       <c r="C15" t="n">
-        <v>772</v>
+        <v>715</v>
       </c>
       <c r="D15" t="n">
-        <v>715</v>
+        <v>591</v>
       </c>
       <c r="E15" t="n">
-        <v>591</v>
+        <v>623</v>
       </c>
       <c r="F15" t="n">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="G15" t="n">
-        <v>618</v>
+        <v>720</v>
       </c>
       <c r="H15" t="n">
-        <v>720</v>
+        <v>672</v>
       </c>
       <c r="I15" t="n">
-        <v>672</v>
+        <v>553</v>
       </c>
       <c r="J15" t="n">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="K15" t="n">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="L15" t="n">
-        <v>587</v>
+        <v>212</v>
       </c>
       <c r="M15" t="n">
-        <v>212</v>
+        <v>171</v>
       </c>
       <c r="N15" t="n">
-        <v>171</v>
+        <v>124</v>
       </c>
       <c r="O15" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="P15" t="n">
+        <v>113</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>167</v>
+      </c>
+      <c r="R15" t="n">
+        <v>176</v>
+      </c>
+      <c r="S15" t="n">
+        <v>132</v>
+      </c>
+      <c r="T15" t="n">
+        <v>161</v>
+      </c>
+      <c r="U15" t="n">
+        <v>175</v>
+      </c>
+      <c r="V15" t="n">
+        <v>37</v>
+      </c>
+      <c r="W15" t="n">
+        <v>35</v>
+      </c>
+      <c r="X15" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>81</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>88</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>76</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>87</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>88</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>69</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>59</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>56</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>54</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>154</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>143</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>125</v>
+      </c>
+      <c r="AN15" t="n">
         <v>122</v>
       </c>
-      <c r="Q15" t="n">
-        <v>113</v>
-      </c>
-      <c r="R15" t="n">
-        <v>167</v>
-      </c>
-      <c r="S15" t="n">
-        <v>176</v>
-      </c>
-      <c r="T15" t="n">
-        <v>132</v>
-      </c>
-      <c r="U15" t="n">
-        <v>161</v>
-      </c>
-      <c r="V15" t="n">
-        <v>175</v>
-      </c>
-      <c r="W15" t="n">
-        <v>37</v>
-      </c>
-      <c r="X15" t="n">
-        <v>35</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>36</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>33</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>28</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>81</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>88</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>76</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>87</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>88</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>69</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>59</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>56</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>54</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>154</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>143</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>125</v>
-      </c>
       <c r="AO15" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="AP15" t="n">
-        <v>129</v>
+        <v>52</v>
       </c>
       <c r="AQ15" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="AR15" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="AS15" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AT15" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="AU15" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AV15" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AW15" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AX15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>23</v>
       </c>
-      <c r="AY15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>21</v>
-      </c>
       <c r="BA15" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="BB15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC15" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BD15" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE15" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2800000</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
           <t>WARMIŃSKO-MAZURSKIE</t>
         </is>
       </c>
+      <c r="B16" t="n">
+        <v>962</v>
+      </c>
       <c r="C16" t="n">
-        <v>962</v>
+        <v>854</v>
       </c>
       <c r="D16" t="n">
-        <v>854</v>
+        <v>771</v>
       </c>
       <c r="E16" t="n">
-        <v>771</v>
+        <v>694</v>
       </c>
       <c r="F16" t="n">
-        <v>694</v>
+        <v>709</v>
       </c>
       <c r="G16" t="n">
-        <v>709</v>
+        <v>912</v>
       </c>
       <c r="H16" t="n">
-        <v>912</v>
+        <v>818</v>
       </c>
       <c r="I16" t="n">
-        <v>818</v>
+        <v>725</v>
       </c>
       <c r="J16" t="n">
-        <v>725</v>
+        <v>672</v>
       </c>
       <c r="K16" t="n">
-        <v>672</v>
+        <v>683</v>
       </c>
       <c r="L16" t="n">
-        <v>683</v>
+        <v>324</v>
       </c>
       <c r="M16" t="n">
-        <v>324</v>
+        <v>305</v>
       </c>
       <c r="N16" t="n">
-        <v>305</v>
+        <v>265</v>
       </c>
       <c r="O16" t="n">
-        <v>265</v>
+        <v>216</v>
       </c>
       <c r="P16" t="n">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="Q16" t="n">
-        <v>209</v>
+        <v>178</v>
       </c>
       <c r="R16" t="n">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="S16" t="n">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="T16" t="n">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="U16" t="n">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="V16" t="n">
-        <v>139</v>
+        <v>48</v>
       </c>
       <c r="W16" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="X16" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="Y16" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="Z16" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="AA16" t="n">
-        <v>35</v>
+        <v>107</v>
       </c>
       <c r="AB16" t="n">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="AC16" t="n">
         <v>91</v>
       </c>
       <c r="AD16" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="AE16" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="AF16" t="n">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="AG16" t="n">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="AH16" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AI16" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AJ16" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="AK16" t="n">
-        <v>29</v>
+        <v>187</v>
       </c>
       <c r="AL16" t="n">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="AM16" t="n">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="AN16" t="n">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="AO16" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AP16" t="n">
-        <v>165</v>
+        <v>50</v>
       </c>
       <c r="AQ16" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AR16" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AS16" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="AT16" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AU16" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="AV16" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="AW16" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AX16" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="AY16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ16" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB16" t="n">
         <v>14</v>
       </c>
-      <c r="BA16" t="n">
-        <v>17</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>11</v>
-      </c>
       <c r="BC16" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BD16" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE16" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3000000</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
           <t>WIELKOPOLSKIE</t>
         </is>
       </c>
+      <c r="B17" t="n">
+        <v>2723</v>
+      </c>
       <c r="C17" t="n">
-        <v>2723</v>
+        <v>2317</v>
       </c>
       <c r="D17" t="n">
-        <v>2317</v>
+        <v>2224</v>
       </c>
       <c r="E17" t="n">
-        <v>2224</v>
+        <v>2248</v>
       </c>
       <c r="F17" t="n">
-        <v>2248</v>
+        <v>2380</v>
       </c>
       <c r="G17" t="n">
-        <v>2380</v>
+        <v>2596</v>
       </c>
       <c r="H17" t="n">
-        <v>2596</v>
+        <v>2205</v>
       </c>
       <c r="I17" t="n">
-        <v>2205</v>
+        <v>2126</v>
       </c>
       <c r="J17" t="n">
-        <v>2126</v>
+        <v>2152</v>
       </c>
       <c r="K17" t="n">
-        <v>2152</v>
+        <v>2270</v>
       </c>
       <c r="L17" t="n">
-        <v>2270</v>
+        <v>631</v>
       </c>
       <c r="M17" t="n">
-        <v>631</v>
+        <v>554</v>
       </c>
       <c r="N17" t="n">
-        <v>554</v>
+        <v>513</v>
       </c>
       <c r="O17" t="n">
-        <v>513</v>
+        <v>492</v>
       </c>
       <c r="P17" t="n">
-        <v>492</v>
+        <v>536</v>
       </c>
       <c r="Q17" t="n">
-        <v>536</v>
+        <v>820</v>
       </c>
       <c r="R17" t="n">
-        <v>820</v>
+        <v>673</v>
       </c>
       <c r="S17" t="n">
-        <v>673</v>
+        <v>564</v>
       </c>
       <c r="T17" t="n">
+        <v>543</v>
+      </c>
+      <c r="U17" t="n">
+        <v>624</v>
+      </c>
+      <c r="V17" t="n">
+        <v>142</v>
+      </c>
+      <c r="W17" t="n">
+        <v>106</v>
+      </c>
+      <c r="X17" t="n">
+        <v>116</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>101</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>104</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>294</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>258</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>253</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>336</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>309</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>166</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>169</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>163</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>131</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>133</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>543</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>445</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>517</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>549</v>
+      </c>
+      <c r="AO17" t="n">
         <v>564</v>
       </c>
-      <c r="U17" t="n">
-        <v>543</v>
-      </c>
-      <c r="V17" t="n">
-        <v>624</v>
-      </c>
-      <c r="W17" t="n">
-        <v>142</v>
-      </c>
-      <c r="X17" t="n">
-        <v>106</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>116</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>101</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>104</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>294</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>258</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>253</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>336</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>309</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>166</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>169</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>163</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>131</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>133</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>543</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>445</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>517</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>549</v>
-      </c>
       <c r="AP17" t="n">
-        <v>564</v>
+        <v>127</v>
       </c>
       <c r="AQ17" t="n">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="AR17" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="AS17" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="AT17" t="n">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="AU17" t="n">
-        <v>110</v>
+        <v>61</v>
       </c>
       <c r="AV17" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="AW17" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="AX17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>69</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>66</v>
+      </c>
+      <c r="BA17" t="n">
         <v>54</v>
       </c>
-      <c r="AY17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>69</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>66</v>
-      </c>
       <c r="BB17" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="BC17" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="BD17" t="n">
-        <v>41</v>
-      </c>
-      <c r="BE17" t="n">
         <v>41</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3200000</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
           <t>ZACHODNIOPOMORSKIE</t>
         </is>
       </c>
+      <c r="B18" t="n">
+        <v>857</v>
+      </c>
       <c r="C18" t="n">
-        <v>857</v>
+        <v>874</v>
       </c>
       <c r="D18" t="n">
-        <v>874</v>
+        <v>831</v>
       </c>
       <c r="E18" t="n">
-        <v>831</v>
+        <v>737</v>
       </c>
       <c r="F18" t="n">
-        <v>737</v>
+        <v>703</v>
       </c>
       <c r="G18" t="n">
-        <v>703</v>
+        <v>801</v>
       </c>
       <c r="H18" t="n">
-        <v>801</v>
+        <v>832</v>
       </c>
       <c r="I18" t="n">
-        <v>832</v>
+        <v>784</v>
       </c>
       <c r="J18" t="n">
-        <v>784</v>
+        <v>700</v>
       </c>
       <c r="K18" t="n">
-        <v>700</v>
+        <v>668</v>
       </c>
       <c r="L18" t="n">
-        <v>668</v>
+        <v>206</v>
       </c>
       <c r="M18" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="N18" t="n">
+        <v>162</v>
+      </c>
+      <c r="O18" t="n">
+        <v>154</v>
+      </c>
+      <c r="P18" t="n">
+        <v>143</v>
+      </c>
+      <c r="Q18" t="n">
         <v>204</v>
       </c>
-      <c r="O18" t="n">
-        <v>162</v>
-      </c>
-      <c r="P18" t="n">
-        <v>154</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>143</v>
-      </c>
       <c r="R18" t="n">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="S18" t="n">
-        <v>217</v>
+        <v>181</v>
       </c>
       <c r="T18" t="n">
-        <v>181</v>
+        <v>144</v>
       </c>
       <c r="U18" t="n">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="V18" t="n">
-        <v>168</v>
+        <v>31</v>
       </c>
       <c r="W18" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="X18" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="Y18" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="Z18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>141</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>136</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>137</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>127</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>129</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>79</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>61</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>72</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>53</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>140</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>174</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>199</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>191</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>147</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>56</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>47</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>37</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>35</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>27</v>
+      </c>
+      <c r="AV18" t="n">
         <v>29</v>
       </c>
-      <c r="AA18" t="n">
-        <v>28</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>141</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>136</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>137</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>127</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>129</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>79</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>61</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>72</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>53</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>140</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>174</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>199</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>191</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>147</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>56</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>42</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>47</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>37</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>35</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>27</v>
-      </c>
       <c r="AW18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>29</v>
       </c>
-      <c r="AX18" t="n">
-        <v>34</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>22</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>19</v>
-      </c>
       <c r="BA18" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="BB18" t="n">
         <v>13</v>
       </c>
       <c r="BC18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BD18" t="n">
-        <v>15</v>
-      </c>
-      <c r="BE18" t="n">
         <v>16</v>
       </c>
     </row>

--- a/dane.xlsx
+++ b/dane.xlsx
@@ -1,37 +1,264 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+  <si>
+    <t>Nazwa</t>
+  </si>
+  <si>
+    <t>ogółem_2020</t>
+  </si>
+  <si>
+    <t>ogółem_2021</t>
+  </si>
+  <si>
+    <t>ogółem_2022</t>
+  </si>
+  <si>
+    <t>ogółem_2023</t>
+  </si>
+  <si>
+    <t>ogółem_2024</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - ogółem_2020</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - ogółem_2021</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - ogółem_2022</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - ogółem_2023</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - ogółem_2024</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - niedostosowanie prędkości do warunków ruchu_2020</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - niedostosowanie prędkości do warunków ruchu_2021</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - niedostosowanie prędkości do warunków ruchu_2022</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - niedostosowanie prędkości do warunków ruchu_2023</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - niedostosowanie prędkości do warunków ruchu_2024</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - nieprzestrzeganie pierwszeństwa przejazdu_2020</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - nieprzestrzeganie pierwszeństwa przejazdu_2021</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - nieprzestrzeganie pierwszeństwa przejazdu_2022</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - nieprzestrzeganie pierwszeństwa przejazdu_2023</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - nieprzestrzeganie pierwszeństwa przejazdu_2024</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - nieprawidłowe wyprzedzanie_2020</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - nieprawidłowe wyprzedzanie_2021</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - nieprawidłowe wyprzedzanie_2022</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - nieprawidłowe wyprzedzanie_2023</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - nieprawidłowe wyprzedzanie_2024</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - nieprawidłowe zachowanie wobec pieszych_2020</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - nieprawidłowe zachowanie wobec pieszych_2021</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - nieprawidłowe zachowanie wobec pieszych_2022</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - nieprawidłowe zachowanie wobec pieszych_2023</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - nieprawidłowe zachowanie wobec pieszych_2024</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - niezachowanie bezpiecznej odległości między pojazdami_2020</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - niezachowanie bezpiecznej odległości między pojazdami_2021</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - niezachowanie bezpiecznej odległości między pojazdami_2022</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - niezachowanie bezpiecznej odległości między pojazdami_2023</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - niezachowanie bezpiecznej odległości między pojazdami_2024</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - pozostałe_2020</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - pozostałe_2021</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - pozostałe_2022</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - pozostałe_2023</t>
+  </si>
+  <si>
+    <t>wina kierujących pojazdami - pozostałe_2024</t>
+  </si>
+  <si>
+    <t>wina pieszych - ogółem_2020</t>
+  </si>
+  <si>
+    <t>wina pieszych - ogółem_2021</t>
+  </si>
+  <si>
+    <t>wina pieszych - ogółem_2022</t>
+  </si>
+  <si>
+    <t>wina pieszych - ogółem_2023</t>
+  </si>
+  <si>
+    <t>wina pieszych - ogółem_2024</t>
+  </si>
+  <si>
+    <t>wina pieszych - nieostrożne wejście na jezdnię_2020</t>
+  </si>
+  <si>
+    <t>wina pieszych - nieostrożne wejście na jezdnię_2021</t>
+  </si>
+  <si>
+    <t>wina pieszych - nieostrożne wejście na jezdnię_2022</t>
+  </si>
+  <si>
+    <t>wina pieszych - nieostrożne wejście na jezdnię_2023</t>
+  </si>
+  <si>
+    <t>wina pieszych - nieostrożne wejście na jezdnię_2024</t>
+  </si>
+  <si>
+    <t>wina pieszych - pozostałe_2020</t>
+  </si>
+  <si>
+    <t>wina pieszych - pozostałe_2021</t>
+  </si>
+  <si>
+    <t>wina pieszych - pozostałe_2022</t>
+  </si>
+  <si>
+    <t>wina pieszych - pozostałe_2023</t>
+  </si>
+  <si>
+    <t>wina pieszych - pozostałe_2024</t>
+  </si>
+  <si>
+    <t>POLSKA</t>
+  </si>
+  <si>
+    <t>DOLNOŚLĄSKIE</t>
+  </si>
+  <si>
+    <t>KUJAWSKO-POMORSKIE</t>
+  </si>
+  <si>
+    <t>LUBELSKIE</t>
+  </si>
+  <si>
+    <t>LUBUSKIE</t>
+  </si>
+  <si>
+    <t>ŁÓDZKIE</t>
+  </si>
+  <si>
+    <t>MAŁOPOLSKIE</t>
+  </si>
+  <si>
+    <t>MAZOWIECKIE</t>
+  </si>
+  <si>
+    <t>OPOLSKIE</t>
+  </si>
+  <si>
+    <t>PODKARPACKIE</t>
+  </si>
+  <si>
+    <t>PODLASKIE</t>
+  </si>
+  <si>
+    <t>POMORSKIE</t>
+  </si>
+  <si>
+    <t>ŚLĄSKIE</t>
+  </si>
+  <si>
+    <t>ŚWIĘTOKRZYSKIE</t>
+  </si>
+  <si>
+    <t>WARMIŃSKO-MAZURSKIE</t>
+  </si>
+  <si>
+    <t>WIELKOPOLSKIE</t>
+  </si>
+  <si>
+    <t>ZACHODNIOPOMORSKIE</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +273,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,3221 +589,3071 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:BD18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Nazwa</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ogółem_2020</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ogółem_2021</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>ogółem_2022</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>ogółem_2023</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>ogółem_2024</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - ogółem_2020</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - ogółem_2021</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - ogółem_2022</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - ogółem_2023</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - ogółem_2024</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - niedostosowanie prędkości do warunków ruchu_2020</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - niedostosowanie prędkości do warunków ruchu_2021</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - niedostosowanie prędkości do warunków ruchu_2022</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - niedostosowanie prędkości do warunków ruchu_2023</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - niedostosowanie prędkości do warunków ruchu_2024</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - nieprzestrzeganie pierwszeństwa przejazdu_2020</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - nieprzestrzeganie pierwszeństwa przejazdu_2021</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - nieprzestrzeganie pierwszeństwa przejazdu_2022</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - nieprzestrzeganie pierwszeństwa przejazdu_2023</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - nieprzestrzeganie pierwszeństwa przejazdu_2024</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - nieprawidłowe wyprzedzanie_2020</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - nieprawidłowe wyprzedzanie_2021</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - nieprawidłowe wyprzedzanie_2022</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - nieprawidłowe wyprzedzanie_2023</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - nieprawidłowe wyprzedzanie_2024</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - nieprawidłowe zachowanie wobec pieszych_2020</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - nieprawidłowe zachowanie wobec pieszych_2021</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - nieprawidłowe zachowanie wobec pieszych_2022</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - nieprawidłowe zachowanie wobec pieszych_2023</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - nieprawidłowe zachowanie wobec pieszych_2024</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - niezachowanie bezpiecznej odległości między pojazdami_2020</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - niezachowanie bezpiecznej odległości między pojazdami_2021</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - niezachowanie bezpiecznej odległości między pojazdami_2022</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - niezachowanie bezpiecznej odległości między pojazdami_2023</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - niezachowanie bezpiecznej odległości między pojazdami_2024</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - pozostałe_2020</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - pozostałe_2021</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - pozostałe_2022</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - pozostałe_2023</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>wina kierujących pojazdami - pozostałe_2024</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>wina pieszych - ogółem_2020</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>wina pieszych - ogółem_2021</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>wina pieszych - ogółem_2022</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>wina pieszych - ogółem_2023</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>wina pieszych - ogółem_2024</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>wina pieszych - nieostrożne wejście na jezdnię_2020</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>wina pieszych - nieostrożne wejście na jezdnię_2021</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>wina pieszych - nieostrożne wejście na jezdnię_2022</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>wina pieszych - nieostrożne wejście na jezdnię_2023</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>wina pieszych - nieostrożne wejście na jezdnię_2024</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>wina pieszych - pozostałe_2020</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>wina pieszych - pozostałe_2021</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>wina pieszych - pozostałe_2022</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>wina pieszych - pozostałe_2023</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>wina pieszych - pozostałe_2024</t>
-        </is>
+    <row r="1" spans="1:56">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>POLSKA</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="2" spans="1:56">
+      <c r="A2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2">
         <v>22384</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>21841</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>20476</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>20065</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>20607</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>20999</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>20623</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>19391</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>19058</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>19636</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>5516</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>5254</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2">
         <v>4473</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2">
         <v>4216</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2">
         <v>4269</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2">
         <v>5708</v>
       </c>
-      <c r="R2" t="n">
+      <c r="R2">
         <v>5566</v>
       </c>
-      <c r="S2" t="n">
+      <c r="S2">
         <v>4530</v>
       </c>
-      <c r="T2" t="n">
+      <c r="T2">
         <v>4576</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U2">
         <v>5169</v>
       </c>
-      <c r="V2" t="n">
+      <c r="V2">
         <v>1036</v>
       </c>
-      <c r="W2" t="n">
+      <c r="W2">
         <v>1012</v>
       </c>
-      <c r="X2" t="n">
+      <c r="X2">
         <v>925</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Y2">
         <v>917</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="Z2">
         <v>938</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AA2">
         <v>2817</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AB2">
         <v>2648</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AC2">
         <v>2835</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AD2">
         <v>3084</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AE2">
         <v>2886</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AF2">
         <v>1535</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AG2">
         <v>1607</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AH2">
         <v>1663</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AI2">
         <v>1538</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AJ2">
         <v>1505</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AK2">
         <v>4387</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AL2">
         <v>4536</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AM2">
         <v>4965</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AN2">
         <v>4727</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AO2">
         <v>4869</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AP2">
         <v>1385</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AQ2">
         <v>1218</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AR2">
         <v>1085</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="AS2">
         <v>1007</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="AT2">
         <v>971</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="AU2">
         <v>830</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AV2">
         <v>759</v>
       </c>
-      <c r="AW2" t="n">
+      <c r="AW2">
         <v>678</v>
       </c>
-      <c r="AX2" t="n">
+      <c r="AX2">
         <v>622</v>
       </c>
-      <c r="AY2" t="n">
+      <c r="AY2">
         <v>558</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="AZ2">
         <v>555</v>
       </c>
-      <c r="BA2" t="n">
+      <c r="BA2">
         <v>459</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BB2">
         <v>407</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BC2">
         <v>385</v>
       </c>
-      <c r="BD2" t="n">
+      <c r="BD2">
         <v>413</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DOLNOŚLĄSKIE</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:56">
+      <c r="A3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3">
         <v>1490</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>1647</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>1808</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>1738</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>1821</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>1393</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>1542</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>1702</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>1651</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>1717</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>375</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>401</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3">
         <v>362</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3">
         <v>379</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3">
         <v>401</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3">
         <v>370</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R3">
         <v>419</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S3">
         <v>398</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T3">
         <v>387</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U3">
         <v>407</v>
       </c>
-      <c r="V3" t="n">
+      <c r="V3">
         <v>60</v>
       </c>
-      <c r="W3" t="n">
+      <c r="W3">
         <v>78</v>
       </c>
-      <c r="X3" t="n">
+      <c r="X3">
         <v>66</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Y3">
         <v>62</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="Z3">
         <v>92</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AA3">
         <v>182</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AB3">
         <v>202</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AC3">
         <v>276</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AD3">
         <v>247</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AE3">
         <v>238</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AF3">
         <v>124</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AG3">
         <v>135</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AH3">
         <v>175</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AI3">
         <v>189</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AJ3">
         <v>173</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AK3">
         <v>282</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AL3">
         <v>307</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AM3">
         <v>425</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AN3">
         <v>387</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AO3">
         <v>406</v>
       </c>
-      <c r="AP3" t="n">
+      <c r="AP3">
         <v>97</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AQ3">
         <v>105</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AR3">
         <v>106</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="AS3">
         <v>87</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="AT3">
         <v>104</v>
       </c>
-      <c r="AU3" t="n">
+      <c r="AU3">
         <v>49</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AV3">
         <v>63</v>
       </c>
-      <c r="AW3" t="n">
+      <c r="AW3">
         <v>55</v>
       </c>
-      <c r="AX3" t="n">
+      <c r="AX3">
         <v>46</v>
       </c>
-      <c r="AY3" t="n">
+      <c r="AY3">
         <v>48</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="AZ3">
         <v>48</v>
       </c>
-      <c r="BA3" t="n">
+      <c r="BA3">
         <v>42</v>
       </c>
-      <c r="BB3" t="n">
+      <c r="BB3">
         <v>51</v>
       </c>
-      <c r="BC3" t="n">
+      <c r="BC3">
         <v>41</v>
       </c>
-      <c r="BD3" t="n">
+      <c r="BD3">
         <v>56</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>KUJAWSKO-POMORSKIE</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:56">
+      <c r="A4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4">
         <v>791</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>774</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>744</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>745</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>746</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>746</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>727</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>709</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>693</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>711</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>205</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>191</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4">
         <v>176</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4">
         <v>115</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4">
         <v>142</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4">
         <v>200</v>
       </c>
-      <c r="R4" t="n">
+      <c r="R4">
         <v>195</v>
       </c>
-      <c r="S4" t="n">
+      <c r="S4">
         <v>186</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T4">
         <v>203</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U4">
         <v>222</v>
       </c>
-      <c r="V4" t="n">
+      <c r="V4">
         <v>33</v>
       </c>
-      <c r="W4" t="n">
+      <c r="W4">
         <v>40</v>
       </c>
-      <c r="X4" t="n">
+      <c r="X4">
         <v>35</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Y4">
         <v>51</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="Z4">
         <v>42</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AA4">
         <v>126</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AB4">
         <v>111</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AC4">
         <v>103</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AD4">
         <v>132</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AE4">
         <v>116</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AF4">
         <v>37</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AG4">
         <v>40</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AH4">
         <v>41</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AI4">
         <v>38</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AJ4">
         <v>48</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AK4">
         <v>145</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AL4">
         <v>150</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AM4">
         <v>168</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AN4">
         <v>154</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AO4">
         <v>141</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AP4">
         <v>45</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AQ4">
         <v>47</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="AR4">
         <v>35</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="AS4">
         <v>52</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="AT4">
         <v>35</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="AU4">
         <v>28</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AV4">
         <v>29</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="AW4">
         <v>26</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="AX4">
         <v>33</v>
       </c>
-      <c r="AY4" t="n">
+      <c r="AY4">
         <v>22</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="AZ4">
         <v>17</v>
       </c>
-      <c r="BA4" t="n">
+      <c r="BA4">
         <v>18</v>
       </c>
-      <c r="BB4" t="n">
+      <c r="BB4">
         <v>9</v>
       </c>
-      <c r="BC4" t="n">
+      <c r="BC4">
         <v>19</v>
       </c>
-      <c r="BD4" t="n">
+      <c r="BD4">
         <v>13</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>LUBELSKIE</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:56">
+      <c r="A5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5">
         <v>897</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>863</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>767</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>763</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>817</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>827</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>799</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>716</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>706</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>770</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>235</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>225</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5">
         <v>184</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5">
         <v>190</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5">
         <v>189</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5">
         <v>203</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R5">
         <v>198</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S5">
         <v>152</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T5">
         <v>173</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U5">
         <v>213</v>
       </c>
-      <c r="V5" t="n">
+      <c r="V5">
         <v>57</v>
       </c>
-      <c r="W5" t="n">
+      <c r="W5">
         <v>57</v>
       </c>
-      <c r="X5" t="n">
+      <c r="X5">
         <v>47</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Y5">
         <v>47</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="Z5">
         <v>43</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AA5">
         <v>106</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AB5">
         <v>113</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AC5">
         <v>93</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AD5">
         <v>101</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AE5">
         <v>106</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AF5">
         <v>41</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AG5">
         <v>44</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AH5">
         <v>43</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AI5">
         <v>38</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AJ5">
         <v>35</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AK5">
         <v>185</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AL5">
         <v>162</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AM5">
         <v>197</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AN5">
         <v>157</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AO5">
         <v>184</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="AP5">
         <v>70</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AQ5">
         <v>64</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="AR5">
         <v>51</v>
       </c>
-      <c r="AS5" t="n">
+      <c r="AS5">
         <v>57</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="AT5">
         <v>47</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="AU5">
         <v>47</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AV5">
         <v>37</v>
       </c>
-      <c r="AW5" t="n">
+      <c r="AW5">
         <v>30</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="AX5">
         <v>35</v>
       </c>
-      <c r="AY5" t="n">
+      <c r="AY5">
         <v>31</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="AZ5">
         <v>23</v>
       </c>
-      <c r="BA5" t="n">
+      <c r="BA5">
         <v>27</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BB5">
         <v>21</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="BC5">
         <v>22</v>
       </c>
-      <c r="BD5" t="n">
+      <c r="BD5">
         <v>16</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>LUBUSKIE</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:56">
+      <c r="A6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6">
         <v>581</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>516</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>483</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>431</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>438</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>551</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>497</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>459</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>419</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>419</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>176</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>142</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6">
         <v>113</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6">
         <v>131</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6">
         <v>122</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6">
         <v>118</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R6">
         <v>108</v>
       </c>
-      <c r="S6" t="n">
+      <c r="S6">
         <v>87</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T6">
         <v>66</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U6">
         <v>104</v>
       </c>
-      <c r="V6" t="n">
+      <c r="V6">
         <v>36</v>
       </c>
-      <c r="W6" t="n">
+      <c r="W6">
         <v>30</v>
       </c>
-      <c r="X6" t="n">
+      <c r="X6">
         <v>48</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Y6">
         <v>30</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="Z6">
         <v>21</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AA6">
         <v>68</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AB6">
         <v>60</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AC6">
         <v>61</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AD6">
         <v>73</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AE6">
         <v>37</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AF6">
         <v>38</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AG6">
         <v>41</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AH6">
         <v>39</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AI6">
         <v>18</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="AJ6">
         <v>29</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AK6">
         <v>115</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AL6">
         <v>116</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AM6">
         <v>111</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AN6">
         <v>101</v>
       </c>
-      <c r="AO6" t="n">
+      <c r="AO6">
         <v>106</v>
       </c>
-      <c r="AP6" t="n">
+      <c r="AP6">
         <v>30</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AQ6">
         <v>19</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="AR6">
         <v>24</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="AS6">
         <v>12</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="AT6">
         <v>19</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="AU6">
         <v>22</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AV6">
         <v>12</v>
       </c>
-      <c r="AW6" t="n">
+      <c r="AW6">
         <v>15</v>
       </c>
-      <c r="AX6" t="n">
+      <c r="AX6">
         <v>9</v>
       </c>
-      <c r="AY6" t="n">
+      <c r="AY6">
         <v>11</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="AZ6">
         <v>8</v>
       </c>
-      <c r="BA6" t="n">
+      <c r="BA6">
         <v>7</v>
       </c>
-      <c r="BB6" t="n">
+      <c r="BB6">
         <v>9</v>
       </c>
-      <c r="BC6" t="n">
+      <c r="BC6">
         <v>3</v>
       </c>
-      <c r="BD6" t="n">
+      <c r="BD6">
         <v>8</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ŁÓDZKIE</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:56">
+      <c r="A7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7">
         <v>2332</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>2208</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>2108</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>2029</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>2106</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>2199</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>2093</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>1997</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>1944</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>2013</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>576</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>518</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7">
         <v>444</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O7">
         <v>391</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P7">
         <v>394</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q7">
         <v>653</v>
       </c>
-      <c r="R7" t="n">
+      <c r="R7">
         <v>577</v>
       </c>
-      <c r="S7" t="n">
+      <c r="S7">
         <v>532</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T7">
         <v>472</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U7">
         <v>549</v>
       </c>
-      <c r="V7" t="n">
+      <c r="V7">
         <v>105</v>
       </c>
-      <c r="W7" t="n">
+      <c r="W7">
         <v>87</v>
       </c>
-      <c r="X7" t="n">
+      <c r="X7">
         <v>63</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Y7">
         <v>75</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="Z7">
         <v>72</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AA7">
         <v>280</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AB7">
         <v>265</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AC7">
         <v>300</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AD7">
         <v>329</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AE7">
         <v>343</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AF7">
         <v>123</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AG7">
         <v>111</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AH7">
         <v>123</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AI7">
         <v>143</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AJ7">
         <v>112</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AK7">
         <v>462</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AL7">
         <v>535</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AM7">
         <v>535</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AN7">
         <v>534</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AO7">
         <v>543</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AP7">
         <v>133</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AQ7">
         <v>115</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AR7">
         <v>111</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="AS7">
         <v>85</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="AT7">
         <v>93</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="AU7">
         <v>89</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AV7">
         <v>74</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="AW7">
         <v>72</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="AX7">
         <v>49</v>
       </c>
-      <c r="AY7" t="n">
+      <c r="AY7">
         <v>49</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="AZ7">
         <v>44</v>
       </c>
-      <c r="BA7" t="n">
+      <c r="BA7">
         <v>41</v>
       </c>
-      <c r="BB7" t="n">
+      <c r="BB7">
         <v>39</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="BC7">
         <v>36</v>
       </c>
-      <c r="BD7" t="n">
+      <c r="BD7">
         <v>44</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>MAŁOPOLSKIE</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:56">
+      <c r="A8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8">
         <v>2089</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>2140</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>2136</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>2108</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>2382</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>1957</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>1978</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>2010</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>1978</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>2258</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>503</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>518</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8">
         <v>477</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O8">
         <v>487</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P8">
         <v>503</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q8">
         <v>443</v>
       </c>
-      <c r="R8" t="n">
+      <c r="R8">
         <v>458</v>
       </c>
-      <c r="S8" t="n">
+      <c r="S8">
         <v>421</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T8">
         <v>396</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U8">
         <v>558</v>
       </c>
-      <c r="V8" t="n">
+      <c r="V8">
         <v>78</v>
       </c>
-      <c r="W8" t="n">
+      <c r="W8">
         <v>75</v>
       </c>
-      <c r="X8" t="n">
+      <c r="X8">
         <v>88</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Y8">
         <v>68</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="Z8">
         <v>74</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AA8">
         <v>285</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AB8">
         <v>258</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AC8">
         <v>287</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AD8">
         <v>301</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AE8">
         <v>302</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AF8">
         <v>194</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AG8">
         <v>198</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AH8">
         <v>218</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AI8">
         <v>203</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AJ8">
         <v>257</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AK8">
         <v>454</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AL8">
         <v>471</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AM8">
         <v>519</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AN8">
         <v>523</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AO8">
         <v>564</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AP8">
         <v>132</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AQ8">
         <v>162</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="AR8">
         <v>126</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="AS8">
         <v>130</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="AT8">
         <v>124</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="AU8">
         <v>72</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AV8">
         <v>110</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="AW8">
         <v>77</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="AX8">
         <v>85</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="AY8">
         <v>63</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="AZ8">
         <v>60</v>
       </c>
-      <c r="BA8" t="n">
+      <c r="BA8">
         <v>52</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BB8">
         <v>49</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="BC8">
         <v>45</v>
       </c>
-      <c r="BD8" t="n">
+      <c r="BD8">
         <v>61</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>MAZOWIECKIE</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:56">
+      <c r="A9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9">
         <v>2880</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>2988</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>2811</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>2723</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>2770</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>2695</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>2828</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>2664</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>2595</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>2628</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>705</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>717</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9">
         <v>613</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9">
         <v>608</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P9">
         <v>587</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q9">
         <v>819</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R9">
         <v>765</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S9">
         <v>607</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T9">
         <v>634</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U9">
         <v>706</v>
       </c>
-      <c r="V9" t="n">
+      <c r="V9">
         <v>162</v>
       </c>
-      <c r="W9" t="n">
+      <c r="W9">
         <v>134</v>
       </c>
-      <c r="X9" t="n">
+      <c r="X9">
         <v>168</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Y9">
         <v>155</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="Z9">
         <v>154</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AA9">
         <v>361</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AB9">
         <v>345</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AC9">
         <v>394</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AD9">
         <v>416</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AE9">
         <v>361</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AF9">
         <v>111</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AG9">
         <v>198</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AH9">
         <v>177</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AI9">
         <v>172</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AJ9">
         <v>136</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AK9">
         <v>537</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AL9">
         <v>669</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AM9">
         <v>705</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AN9">
         <v>610</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AO9">
         <v>684</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AP9">
         <v>185</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AQ9">
         <v>160</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="AR9">
         <v>147</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="AS9">
         <v>128</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="AT9">
         <v>142</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="AU9">
         <v>102</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AV9">
         <v>86</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="AW9">
         <v>83</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="AX9">
         <v>76</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="AY9">
         <v>74</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="AZ9">
         <v>83</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BA9">
         <v>74</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BB9">
         <v>64</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BC9">
         <v>52</v>
       </c>
-      <c r="BD9" t="n">
+      <c r="BD9">
         <v>68</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>OPOLSKIE</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:56">
+      <c r="A10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10">
         <v>466</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>520</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>427</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>447</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>468</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>451</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>504</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>413</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>436</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>456</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>89</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>112</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10">
         <v>92</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10">
         <v>90</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P10">
         <v>93</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q10">
         <v>117</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R10">
         <v>150</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S10">
         <v>87</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T10">
         <v>113</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U10">
         <v>117</v>
       </c>
-      <c r="V10" t="n">
+      <c r="V10">
         <v>25</v>
       </c>
-      <c r="W10" t="n">
+      <c r="W10">
         <v>30</v>
       </c>
-      <c r="X10" t="n">
+      <c r="X10">
         <v>18</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Y10">
         <v>30</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="Z10">
         <v>32</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AA10">
         <v>51</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AB10">
         <v>47</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AC10">
         <v>49</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AD10">
         <v>54</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AE10">
         <v>54</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AF10">
         <v>58</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AG10">
         <v>51</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AH10">
         <v>45</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AI10">
         <v>44</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AJ10">
         <v>59</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AK10">
         <v>111</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AL10">
         <v>114</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AM10">
         <v>122</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AN10">
         <v>105</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AO10">
         <v>101</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AP10">
         <v>15</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AQ10">
         <v>16</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="AR10">
         <v>14</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="AS10">
         <v>11</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="AT10">
         <v>12</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="AU10">
         <v>8</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AV10">
         <v>12</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="AW10">
         <v>7</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="AX10">
         <v>7</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="AY10">
         <v>8</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="AZ10">
         <v>7</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BA10">
         <v>4</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BB10">
         <v>7</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BC10">
         <v>4</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="BD10">
         <v>4</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>PODKARPACKIE</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:56">
+      <c r="A11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11">
         <v>1114</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>1181</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>1009</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>1140</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>981</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>1032</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>1116</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>952</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>1078</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>949</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>317</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>323</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11">
         <v>256</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O11">
         <v>223</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P11">
         <v>221</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q11">
         <v>311</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R11">
         <v>313</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S11">
         <v>214</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T11">
         <v>285</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U11">
         <v>231</v>
       </c>
-      <c r="V11" t="n">
+      <c r="V11">
         <v>39</v>
       </c>
-      <c r="W11" t="n">
+      <c r="W11">
         <v>56</v>
       </c>
-      <c r="X11" t="n">
+      <c r="X11">
         <v>35</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Y11">
         <v>54</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="Z11">
         <v>36</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AA11">
         <v>87</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AB11">
         <v>91</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AC11">
         <v>99</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AD11">
         <v>121</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AE11">
         <v>102</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AF11">
         <v>79</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AG11">
         <v>118</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AH11">
         <v>110</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AI11">
         <v>129</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AJ11">
         <v>99</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AK11">
         <v>199</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AL11">
         <v>215</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AM11">
         <v>238</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AN11">
         <v>266</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AO11">
         <v>260</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AP11">
         <v>82</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AQ11">
         <v>65</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="AR11">
         <v>57</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="AS11">
         <v>62</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="AT11">
         <v>32</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="AU11">
         <v>59</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AV11">
         <v>46</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="AW11">
         <v>46</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="AX11">
         <v>47</v>
       </c>
-      <c r="AY11" t="n">
+      <c r="AY11">
         <v>23</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="AZ11">
         <v>23</v>
       </c>
-      <c r="BA11" t="n">
+      <c r="BA11">
         <v>19</v>
       </c>
-      <c r="BB11" t="n">
+      <c r="BB11">
         <v>11</v>
       </c>
-      <c r="BC11" t="n">
+      <c r="BC11">
         <v>15</v>
       </c>
-      <c r="BD11" t="n">
+      <c r="BD11">
         <v>9</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>PODLASKIE</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:56">
+      <c r="A12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12">
         <v>417</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>418</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>321</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>329</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>338</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>393</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>400</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>310</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>314</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>325</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>117</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>95</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12">
         <v>79</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O12">
         <v>68</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P12">
         <v>72</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q12">
         <v>102</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R12">
         <v>121</v>
       </c>
-      <c r="S12" t="n">
+      <c r="S12">
         <v>65</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T12">
         <v>87</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U12">
         <v>94</v>
       </c>
-      <c r="V12" t="n">
+      <c r="V12">
         <v>17</v>
       </c>
-      <c r="W12" t="n">
+      <c r="W12">
         <v>25</v>
       </c>
-      <c r="X12" t="n">
+      <c r="X12">
         <v>18</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Y12">
         <v>21</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="Z12">
         <v>23</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AA12">
         <v>56</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AB12">
         <v>54</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AC12">
         <v>49</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AD12">
         <v>56</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AE12">
         <v>49</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AF12">
         <v>20</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AG12">
         <v>20</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AH12">
         <v>22</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AI12">
         <v>9</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AJ12">
         <v>14</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AK12">
         <v>81</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AL12">
         <v>85</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AM12">
         <v>77</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AN12">
         <v>73</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AO12">
         <v>73</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AP12">
         <v>24</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AQ12">
         <v>18</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="AR12">
         <v>11</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="AS12">
         <v>15</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="AT12">
         <v>13</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="AU12">
         <v>16</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AV12">
         <v>9</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="AW12">
         <v>5</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="AX12">
         <v>6</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="AY12">
         <v>9</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="AZ12">
         <v>8</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BA12">
         <v>9</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BB12">
         <v>6</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BC12">
         <v>9</v>
       </c>
-      <c r="BD12" t="n">
+      <c r="BD12">
         <v>4</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>POMORSKIE</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+    <row r="13" spans="1:56">
+      <c r="A13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13">
         <v>1748</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>1699</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>1523</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>1492</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>1618</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>1639</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>1623</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>1461</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>1435</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13">
         <v>1554</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13">
         <v>474</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13">
         <v>449</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N13">
         <v>353</v>
       </c>
-      <c r="O13" t="n">
+      <c r="O13">
         <v>345</v>
       </c>
-      <c r="P13" t="n">
+      <c r="P13">
         <v>379</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="Q13">
         <v>419</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R13">
         <v>431</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S13">
         <v>308</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T13">
         <v>343</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U13">
         <v>388</v>
       </c>
-      <c r="V13" t="n">
+      <c r="V13">
         <v>86</v>
       </c>
-      <c r="W13" t="n">
+      <c r="W13">
         <v>80</v>
       </c>
-      <c r="X13" t="n">
+      <c r="X13">
         <v>47</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="Y13">
         <v>58</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="Z13">
         <v>88</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AA13">
         <v>220</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AB13">
         <v>237</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AC13">
         <v>228</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AD13">
         <v>246</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AE13">
         <v>215</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AF13">
         <v>112</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AG13">
         <v>104</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AH13">
         <v>123</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AI13">
         <v>99</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AJ13">
         <v>107</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AK13">
         <v>328</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AL13">
         <v>322</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AM13">
         <v>402</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AN13">
         <v>344</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AO13">
         <v>377</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AP13">
         <v>109</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AQ13">
         <v>76</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="AR13">
         <v>62</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="AS13">
         <v>57</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="AT13">
         <v>64</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="AU13">
         <v>72</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="AV13">
         <v>51</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="AW13">
         <v>45</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="AX13">
         <v>39</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="AY13">
         <v>40</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="AZ13">
         <v>37</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BA13">
         <v>25</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BB13">
         <v>17</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BC13">
         <v>18</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BD13">
         <v>24</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>ŚLĄSKIE</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+    <row r="14" spans="1:56">
+      <c r="A14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14">
         <v>2265</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>2127</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>1922</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>1818</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>1712</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>2087</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>1989</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>1810</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14">
         <v>1704</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14">
         <v>1628</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14">
         <v>371</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14">
         <v>329</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N14">
         <v>260</v>
       </c>
-      <c r="O14" t="n">
+      <c r="O14">
         <v>205</v>
       </c>
-      <c r="P14" t="n">
+      <c r="P14">
         <v>165</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="Q14">
         <v>584</v>
       </c>
-      <c r="R14" t="n">
+      <c r="R14">
         <v>612</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S14">
         <v>463</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T14">
         <v>457</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U14">
         <v>474</v>
       </c>
-      <c r="V14" t="n">
+      <c r="V14">
         <v>80</v>
       </c>
-      <c r="W14" t="n">
+      <c r="W14">
         <v>90</v>
       </c>
-      <c r="X14" t="n">
+      <c r="X14">
         <v>70</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="Y14">
         <v>70</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="Z14">
         <v>66</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AA14">
         <v>372</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AB14">
         <v>292</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AC14">
         <v>339</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AD14">
         <v>360</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AE14">
         <v>331</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AF14">
         <v>216</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AG14">
         <v>215</v>
       </c>
-      <c r="AH14" t="n">
+      <c r="AH14">
         <v>211</v>
       </c>
-      <c r="AI14" t="n">
+      <c r="AI14">
         <v>170</v>
       </c>
-      <c r="AJ14" t="n">
+      <c r="AJ14">
         <v>167</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AK14">
         <v>464</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AL14">
         <v>451</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AM14">
         <v>467</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="AN14">
         <v>442</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="AO14">
         <v>425</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="AP14">
         <v>178</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="AQ14">
         <v>138</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="AR14">
         <v>112</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="AS14">
         <v>114</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="AT14">
         <v>84</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="AU14">
         <v>116</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="AV14">
         <v>91</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="AW14">
         <v>74</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="AX14">
         <v>77</v>
       </c>
-      <c r="AY14" t="n">
+      <c r="AY14">
         <v>57</v>
       </c>
-      <c r="AZ14" t="n">
+      <c r="AZ14">
         <v>62</v>
       </c>
-      <c r="BA14" t="n">
+      <c r="BA14">
         <v>47</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="BB14">
         <v>38</v>
       </c>
-      <c r="BC14" t="n">
+      <c r="BC14">
         <v>37</v>
       </c>
-      <c r="BD14" t="n">
+      <c r="BD14">
         <v>27</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ŚWIĘTOKRZYSKIE</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+    <row r="15" spans="1:56">
+      <c r="A15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15">
         <v>772</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>715</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>591</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>623</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>618</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>720</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>672</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>553</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15">
         <v>581</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15">
         <v>587</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15">
         <v>212</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15">
         <v>171</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N15">
         <v>124</v>
       </c>
-      <c r="O15" t="n">
+      <c r="O15">
         <v>122</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P15">
         <v>113</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q15">
         <v>167</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R15">
         <v>176</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S15">
         <v>132</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T15">
         <v>161</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U15">
         <v>175</v>
       </c>
-      <c r="V15" t="n">
+      <c r="V15">
         <v>37</v>
       </c>
-      <c r="W15" t="n">
+      <c r="W15">
         <v>35</v>
       </c>
-      <c r="X15" t="n">
+      <c r="X15">
         <v>36</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="Y15">
         <v>33</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="Z15">
         <v>28</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AA15">
         <v>81</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AB15">
         <v>88</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AC15">
         <v>76</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AD15">
         <v>87</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AE15">
         <v>88</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AF15">
         <v>69</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AG15">
         <v>59</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AH15">
         <v>60</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AI15">
         <v>56</v>
       </c>
-      <c r="AJ15" t="n">
+      <c r="AJ15">
         <v>54</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AK15">
         <v>154</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AL15">
         <v>143</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AM15">
         <v>125</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AN15">
         <v>122</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="AO15">
         <v>129</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AP15">
         <v>52</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AQ15">
         <v>43</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="AR15">
         <v>38</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="AS15">
         <v>42</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="AT15">
         <v>31</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="AU15">
         <v>29</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="AV15">
         <v>27</v>
       </c>
-      <c r="AW15" t="n">
+      <c r="AW15">
         <v>23</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="AX15">
         <v>24</v>
       </c>
-      <c r="AY15" t="n">
+      <c r="AY15">
         <v>21</v>
       </c>
-      <c r="AZ15" t="n">
+      <c r="AZ15">
         <v>23</v>
       </c>
-      <c r="BA15" t="n">
+      <c r="BA15">
         <v>16</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="BB15">
         <v>15</v>
       </c>
-      <c r="BC15" t="n">
+      <c r="BC15">
         <v>18</v>
       </c>
-      <c r="BD15" t="n">
+      <c r="BD15">
         <v>10</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>WARMIŃSKO-MAZURSKIE</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+    <row r="16" spans="1:56">
+      <c r="A16" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16">
         <v>962</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>854</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>771</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>694</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>709</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>912</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>818</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>725</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16">
         <v>672</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16">
         <v>683</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16">
         <v>324</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16">
         <v>305</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N16">
         <v>265</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O16">
         <v>216</v>
       </c>
-      <c r="P16" t="n">
+      <c r="P16">
         <v>209</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="Q16">
         <v>178</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R16">
         <v>153</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S16">
         <v>133</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T16">
         <v>112</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U16">
         <v>139</v>
       </c>
-      <c r="V16" t="n">
+      <c r="V16">
         <v>48</v>
       </c>
-      <c r="W16" t="n">
+      <c r="W16">
         <v>49</v>
       </c>
-      <c r="X16" t="n">
+      <c r="X16">
         <v>37</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="Y16">
         <v>33</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="Z16">
         <v>35</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AA16">
         <v>107</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AB16">
         <v>91</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AC16">
         <v>91</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AD16">
         <v>98</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AE16">
         <v>106</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AF16">
         <v>68</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AG16">
         <v>43</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AH16">
         <v>41</v>
       </c>
-      <c r="AI16" t="n">
+      <c r="AI16">
         <v>44</v>
       </c>
-      <c r="AJ16" t="n">
+      <c r="AJ16">
         <v>29</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AK16">
         <v>187</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AL16">
         <v>177</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AM16">
         <v>158</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="AN16">
         <v>169</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="AO16">
         <v>165</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AP16">
         <v>50</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AQ16">
         <v>36</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="AR16">
         <v>46</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="AS16">
         <v>22</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="AT16">
         <v>26</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="AU16">
         <v>33</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="AV16">
         <v>25</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="AW16">
         <v>32</v>
       </c>
-      <c r="AX16" t="n">
+      <c r="AX16">
         <v>12</v>
       </c>
-      <c r="AY16" t="n">
+      <c r="AY16">
         <v>14</v>
       </c>
-      <c r="AZ16" t="n">
+      <c r="AZ16">
         <v>17</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="BA16">
         <v>11</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BB16">
         <v>14</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BC16">
         <v>10</v>
       </c>
-      <c r="BD16" t="n">
+      <c r="BD16">
         <v>12</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>WIELKOPOLSKIE</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
+    <row r="17" spans="1:56">
+      <c r="A17" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17">
         <v>2723</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>2317</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>2224</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>2248</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>2380</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>2596</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>2205</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17">
         <v>2126</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17">
         <v>2152</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17">
         <v>2270</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17">
         <v>631</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17">
         <v>554</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N17">
         <v>513</v>
       </c>
-      <c r="O17" t="n">
+      <c r="O17">
         <v>492</v>
       </c>
-      <c r="P17" t="n">
+      <c r="P17">
         <v>536</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="Q17">
         <v>820</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R17">
         <v>673</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S17">
         <v>564</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T17">
         <v>543</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U17">
         <v>624</v>
       </c>
-      <c r="V17" t="n">
+      <c r="V17">
         <v>142</v>
       </c>
-      <c r="W17" t="n">
+      <c r="W17">
         <v>106</v>
       </c>
-      <c r="X17" t="n">
+      <c r="X17">
         <v>116</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="Y17">
         <v>101</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="Z17">
         <v>104</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AA17">
         <v>294</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AB17">
         <v>258</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AC17">
         <v>253</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AD17">
         <v>336</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AE17">
         <v>309</v>
       </c>
-      <c r="AF17" t="n">
+      <c r="AF17">
         <v>166</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AG17">
         <v>169</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AH17">
         <v>163</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AI17">
         <v>131</v>
       </c>
-      <c r="AJ17" t="n">
+      <c r="AJ17">
         <v>133</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AK17">
         <v>543</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AL17">
         <v>445</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="AM17">
         <v>517</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="AN17">
         <v>549</v>
       </c>
-      <c r="AO17" t="n">
+      <c r="AO17">
         <v>564</v>
       </c>
-      <c r="AP17" t="n">
+      <c r="AP17">
         <v>127</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AQ17">
         <v>112</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="AR17">
         <v>98</v>
       </c>
-      <c r="AS17" t="n">
+      <c r="AS17">
         <v>96</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="AT17">
         <v>110</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="AU17">
         <v>61</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="AV17">
         <v>58</v>
       </c>
-      <c r="AW17" t="n">
+      <c r="AW17">
         <v>54</v>
       </c>
-      <c r="AX17" t="n">
+      <c r="AX17">
         <v>55</v>
       </c>
-      <c r="AY17" t="n">
+      <c r="AY17">
         <v>69</v>
       </c>
-      <c r="AZ17" t="n">
+      <c r="AZ17">
         <v>66</v>
       </c>
-      <c r="BA17" t="n">
+      <c r="BA17">
         <v>54</v>
       </c>
-      <c r="BB17" t="n">
+      <c r="BB17">
         <v>44</v>
       </c>
-      <c r="BC17" t="n">
+      <c r="BC17">
         <v>41</v>
       </c>
-      <c r="BD17" t="n">
+      <c r="BD17">
         <v>41</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ZACHODNIOPOMORSKIE</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
+    <row r="18" spans="1:56">
+      <c r="A18" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18">
         <v>857</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>874</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>831</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>737</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18">
         <v>703</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18">
         <v>801</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18">
         <v>832</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18">
         <v>784</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18">
         <v>700</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18">
         <v>668</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18">
         <v>206</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M18">
         <v>204</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N18">
         <v>162</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O18">
         <v>154</v>
       </c>
-      <c r="P18" t="n">
+      <c r="P18">
         <v>143</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Q18">
         <v>204</v>
       </c>
-      <c r="R18" t="n">
+      <c r="R18">
         <v>217</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S18">
         <v>181</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T18">
         <v>144</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U18">
         <v>168</v>
       </c>
-      <c r="V18" t="n">
+      <c r="V18">
         <v>31</v>
       </c>
-      <c r="W18" t="n">
+      <c r="W18">
         <v>40</v>
       </c>
-      <c r="X18" t="n">
+      <c r="X18">
         <v>33</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Y18">
         <v>29</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="Z18">
         <v>28</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AA18">
         <v>141</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AB18">
         <v>136</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AC18">
         <v>137</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AD18">
         <v>127</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AE18">
         <v>129</v>
       </c>
-      <c r="AF18" t="n">
+      <c r="AF18">
         <v>79</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AG18">
         <v>61</v>
       </c>
-      <c r="AH18" t="n">
+      <c r="AH18">
         <v>72</v>
       </c>
-      <c r="AI18" t="n">
+      <c r="AI18">
         <v>55</v>
       </c>
-      <c r="AJ18" t="n">
+      <c r="AJ18">
         <v>53</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AK18">
         <v>140</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AL18">
         <v>174</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="AM18">
         <v>199</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="AN18">
         <v>191</v>
       </c>
-      <c r="AO18" t="n">
+      <c r="AO18">
         <v>147</v>
       </c>
-      <c r="AP18" t="n">
+      <c r="AP18">
         <v>56</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AQ18">
         <v>42</v>
       </c>
-      <c r="AR18" t="n">
+      <c r="AR18">
         <v>47</v>
       </c>
-      <c r="AS18" t="n">
+      <c r="AS18">
         <v>37</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="AT18">
         <v>35</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="AU18">
         <v>27</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="AV18">
         <v>29</v>
       </c>
-      <c r="AW18" t="n">
+      <c r="AW18">
         <v>34</v>
       </c>
-      <c r="AX18" t="n">
+      <c r="AX18">
         <v>22</v>
       </c>
-      <c r="AY18" t="n">
+      <c r="AY18">
         <v>19</v>
       </c>
-      <c r="AZ18" t="n">
+      <c r="AZ18">
         <v>29</v>
       </c>
-      <c r="BA18" t="n">
+      <c r="BA18">
         <v>13</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BB18">
         <v>13</v>
       </c>
-      <c r="BC18" t="n">
+      <c r="BC18">
         <v>15</v>
       </c>
-      <c r="BD18" t="n">
+      <c r="BD18">
         <v>16</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>